--- a/data/NETCD (TRY).xlsx
+++ b/data/NETCD (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -447,22 +451,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>1067348940</v>
+        <v>702654985</v>
       </c>
       <c r="C3">
-        <v>520596456</v>
+        <v>1142206406.247692</v>
       </c>
       <c r="D3">
-        <v>9725553.544407552</v>
+        <v>557107976</v>
       </c>
       <c r="E3">
-        <v>189907621.64008912</v>
+        <v>10407645.659653958</v>
       </c>
       <c r="F3">
-        <v>76631353.08473457</v>
+        <v>203226605.56778425</v>
       </c>
       <c r="G3">
-        <v>124805286.82846384</v>
+        <v>82005817.52843888</v>
+      </c>
+      <c r="H3">
+        <v>133558382.64949426</v>
       </c>
     </row>
     <row r="4">
@@ -474,8 +481,8 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
-      <c r="D5">
-        <v>247124747.2646753</v>
+      <c r="E5">
+        <v>264456597.92200094</v>
       </c>
     </row>
     <row r="6">
@@ -488,22 +495,25 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>732627470</v>
+        <v>701635864</v>
       </c>
       <c r="C7">
-        <v>685692050</v>
+        <v>784009575.7503997</v>
       </c>
       <c r="D7">
-        <v>608576220.4996763</v>
+        <v>733782387</v>
       </c>
       <c r="E7">
-        <v>617510676.1461295</v>
+        <v>651258114.0941015</v>
       </c>
       <c r="F7">
-        <v>495907471.1821443</v>
+        <v>660819178.984197</v>
       </c>
       <c r="G7">
-        <v>444841223.45157725</v>
+        <v>530687453.05573446</v>
+      </c>
+      <c r="H7">
+        <v>476039724.3561722</v>
       </c>
     </row>
     <row r="8">
@@ -521,22 +531,25 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>9145265</v>
+        <v>8292798</v>
       </c>
       <c r="C10">
-        <v>8094007</v>
+        <v>9786659.149942847</v>
       </c>
       <c r="D10">
-        <v>10195593.00821449</v>
+        <v>8661672</v>
       </c>
       <c r="E10">
-        <v>2324702.0865029157</v>
+        <v>10910650.878124982</v>
       </c>
       <c r="F10">
-        <v>1343642.8284578968</v>
+        <v>2487742.776810184</v>
       </c>
       <c r="G10">
-        <v>1513197.543546308</v>
+        <v>1437877.8943401382</v>
+      </c>
+      <c r="H10">
+        <v>1619324.162308967</v>
       </c>
     </row>
     <row r="11">
@@ -544,13 +557,16 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
       </c>
       <c r="B11">
-        <v>148718826</v>
+        <v>213328666</v>
       </c>
       <c r="C11">
-        <v>69630124</v>
-      </c>
-      <c r="E11">
-        <v>37316120.24744797</v>
+        <v>159149074.3288093</v>
+      </c>
+      <c r="D11">
+        <v>74513564</v>
+      </c>
+      <c r="F11">
+        <v>39933249.57341906</v>
       </c>
     </row>
     <row r="12">
@@ -568,22 +584,25 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
-        <v>295726</v>
+        <v>304129</v>
       </c>
       <c r="C14">
-        <v>351279</v>
+        <v>316466.4516310898</v>
       </c>
       <c r="D14">
-        <v>362675.82568409544</v>
+        <v>375916</v>
       </c>
       <c r="E14">
-        <v>233323.5859437031</v>
+        <v>388111.73737385735</v>
       </c>
       <c r="F14">
-        <v>597370.575133196</v>
+        <v>249687.50575007047</v>
       </c>
       <c r="G14">
-        <v>759750.4125717952</v>
+        <v>639266.5718307685</v>
+      </c>
+      <c r="H14">
+        <v>813034.7591752248</v>
       </c>
     </row>
     <row r="15">
@@ -601,22 +620,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>16696545</v>
+        <v>12980116</v>
       </c>
       <c r="C17">
-        <v>8842058</v>
+        <v>17867540.73246456</v>
       </c>
       <c r="D17">
-        <v>6080518.18246506</v>
+        <v>9462187</v>
       </c>
       <c r="E17">
-        <v>6868885.00429441</v>
+        <v>6506969.334055987</v>
       </c>
       <c r="F17">
-        <v>3932841.2015490523</v>
+        <v>7350627.48615629</v>
       </c>
       <c r="G17">
-        <v>3280154.7082994278</v>
+        <v>4208667.144190163</v>
+      </c>
+      <c r="H17">
+        <v>3510205.1268286603</v>
       </c>
     </row>
     <row r="18">
@@ -639,22 +661,25 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>11750511</v>
+        <v>18003558</v>
       </c>
       <c r="C21">
-        <v>11733772</v>
+        <v>12574621.511203237</v>
       </c>
       <c r="D21">
-        <v>143225801.0602099</v>
+        <v>12556708</v>
       </c>
       <c r="E21">
-        <v>36153826.976353705</v>
+        <v>153270801.49714604</v>
       </c>
       <c r="F21">
-        <v>30110484.509850852</v>
+        <v>38689440.00896448</v>
       </c>
       <c r="G21">
-        <v>53784187.38619989</v>
+        <v>32222253.673080463</v>
+      </c>
+      <c r="H21">
+        <v>57556288.374956205</v>
       </c>
     </row>
     <row r="22">
@@ -672,22 +697,25 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>1986583283</v>
+        <v>1657200116</v>
       </c>
       <c r="C24">
-        <v>1304939746</v>
+        <v>2125910344.1721427</v>
       </c>
       <c r="D24">
-        <v>1025291109.3853327</v>
+        <v>1396460410</v>
       </c>
       <c r="E24">
-        <v>890315155.6867613</v>
+        <v>1097198891.1224573</v>
       </c>
       <c r="F24">
-        <v>608523163.3818699</v>
+        <v>952756531.9030813</v>
       </c>
       <c r="G24">
-        <v>628983800.3306586</v>
+        <v>651201335.8676149</v>
+      </c>
+      <c r="H24">
+        <v>673096959.4289355</v>
       </c>
     </row>
     <row r="25">
@@ -700,16 +728,19 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B26">
-        <v>27188059</v>
+        <v>28763230</v>
       </c>
       <c r="C26">
-        <v>28953990</v>
+        <v>29094866.72956289</v>
       </c>
       <c r="D26">
-        <v>12799347.839226423</v>
+        <v>30984650</v>
       </c>
       <c r="E26">
-        <v>14470824.955106478</v>
+        <v>13697017.488729576</v>
+      </c>
+      <c r="F26">
+        <v>15485722.00522501</v>
       </c>
     </row>
     <row r="27">
@@ -721,8 +752,8 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
-      <c r="G28">
-        <v>2732376.685372503</v>
+      <c r="H28">
+        <v>2924009.231989594</v>
       </c>
     </row>
     <row r="29">
@@ -735,22 +766,25 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B30">
-        <v>391562</v>
+        <v>552827</v>
       </c>
       <c r="C30">
-        <v>368710</v>
+        <v>419023.8150638523</v>
       </c>
       <c r="D30">
-        <v>470893.8346410392</v>
+        <v>394569</v>
       </c>
       <c r="E30">
-        <v>262956.85110718384</v>
+        <v>503919.509761762</v>
       </c>
       <c r="F30">
-        <v>419165.35534951685</v>
+        <v>281399.0707681275</v>
       </c>
       <c r="G30">
-        <v>637987.6401898301</v>
+        <v>448563.1045432138</v>
+      </c>
+      <c r="H30">
+        <v>682732.2747251441</v>
       </c>
     </row>
     <row r="31">
@@ -798,22 +832,25 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>56693184</v>
+        <v>65464213</v>
       </c>
       <c r="C39">
-        <v>58183022</v>
+        <v>60669304.600030005</v>
       </c>
       <c r="D39">
-        <v>50422834.14657195</v>
+        <v>62263630</v>
       </c>
       <c r="E39">
-        <v>43067714.84046934</v>
+        <v>53959189.93780924</v>
       </c>
       <c r="F39">
-        <v>46560378.632569306</v>
+        <v>46088226.58617422</v>
       </c>
       <c r="G39">
-        <v>85975738.95730008</v>
+        <v>49825844.91201051</v>
+      </c>
+      <c r="H39">
+        <v>92005562.69715077</v>
       </c>
     </row>
     <row r="40">
@@ -821,22 +858,25 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
-        <v>52450635</v>
+        <v>53695239</v>
       </c>
       <c r="C40">
-        <v>55897487</v>
+        <v>56129208.60609972</v>
       </c>
       <c r="D40">
-        <v>72426154.7678144</v>
+        <v>59817803</v>
       </c>
       <c r="E40">
-        <v>73465106.46723983</v>
+        <v>77505691.77094458</v>
       </c>
       <c r="F40">
-        <v>58294275.514364965</v>
+        <v>78617509.32412982</v>
       </c>
       <c r="G40">
-        <v>56170105.21486568</v>
+        <v>62382687.090199046</v>
+      </c>
+      <c r="H40">
+        <v>60109540.19968996</v>
       </c>
     </row>
     <row r="41">
@@ -844,22 +884,25 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
-        <v>1844098153</v>
+        <v>1982549409</v>
       </c>
       <c r="C41">
-        <v>1780558457</v>
+        <v>1973432159.970231</v>
       </c>
       <c r="D41">
-        <v>1635613867.1274881</v>
+        <v>1905436170</v>
       </c>
       <c r="E41">
-        <v>1472942695.2008584</v>
+        <v>1750326034.1276755</v>
       </c>
       <c r="F41">
-        <v>1208362750.7974353</v>
+        <v>1576246079.8379226</v>
       </c>
       <c r="G41">
-        <v>1120201477.274155</v>
+        <v>1293110081.7244585</v>
+      </c>
+      <c r="H41">
+        <v>1198765704.1479502</v>
       </c>
     </row>
     <row r="42">
@@ -867,22 +910,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B42">
-        <v>1974845</v>
+        <v>3051316</v>
       </c>
       <c r="C42">
-        <v>845560</v>
+        <v>2113348.808259671</v>
       </c>
       <c r="D42">
-        <v>2897553.898284044</v>
+        <v>904862</v>
       </c>
       <c r="E42">
-        <v>30012.91076789978</v>
+        <v>3100770.9859795324</v>
       </c>
       <c r="F42">
-        <v>97060.66080624373</v>
+        <v>32117.83669287709</v>
       </c>
       <c r="G42">
-        <v>138800.8101044779</v>
+        <v>103867.91461799349</v>
+      </c>
+      <c r="H42">
+        <v>148535.46816067857</v>
       </c>
     </row>
     <row r="43">
@@ -905,19 +951,22 @@
         <v xml:space="preserve">    Diğer Duran Varlıklar</v>
       </c>
       <c r="B46">
-        <v>28802682</v>
+        <v>28440583</v>
       </c>
       <c r="C46">
-        <v>24845370</v>
+        <v>30822729.7227794</v>
       </c>
       <c r="D46">
-        <v>37829220.871223144</v>
+        <v>26587875</v>
       </c>
       <c r="E46">
+        <v>40482336.00388452</v>
+      </c>
+      <c r="F46">
         <v>0</v>
       </c>
-      <c r="G46">
-        <v>87014007.37170127</v>
+      <c r="H46">
+        <v>93116649.04378983</v>
       </c>
     </row>
     <row r="47">
@@ -925,22 +974,25 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>2011599120</v>
+        <v>2162516817</v>
       </c>
       <c r="C47">
-        <v>1949652596</v>
+        <v>2152680642.2520266</v>
       </c>
       <c r="D47">
-        <v>1812459872.4852488</v>
+        <v>2086389559</v>
       </c>
       <c r="E47">
-        <v>1604239311.225549</v>
+        <v>1939574959.8247843</v>
       </c>
       <c r="F47">
-        <v>1313733630.9605253</v>
+        <v>1716751054.6609125</v>
       </c>
       <c r="G47">
-        <v>1352870493.9536889</v>
+        <v>1405871044.745829</v>
+      </c>
+      <c r="H47">
+        <v>1447752733.063456</v>
       </c>
     </row>
     <row r="48">
@@ -948,22 +1000,25 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>3998182403</v>
+        <v>3819716933</v>
       </c>
       <c r="C48">
-        <v>3254592342</v>
+        <v>4278590986.424169</v>
       </c>
       <c r="D48">
-        <v>2837750981.8705816</v>
+        <v>3482849969</v>
       </c>
       <c r="E48">
-        <v>2494554466.91231</v>
+        <v>3036773850.947242</v>
       </c>
       <c r="F48">
-        <v>1922256794.342395</v>
+        <v>2669507586.5639935</v>
       </c>
       <c r="G48">
-        <v>1981854294.2843473</v>
+        <v>2057072380.6134439</v>
+      </c>
+      <c r="H48">
+        <v>2120849692.4923916</v>
       </c>
     </row>
     <row r="49">
@@ -976,22 +1031,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>23795270</v>
+        <v>32149175</v>
       </c>
       <c r="C50">
-        <v>24513697</v>
+        <v>25464127.81596384</v>
       </c>
       <c r="D50">
-        <v>33559333.82066511</v>
+        <v>26232941</v>
       </c>
       <c r="E50">
-        <v>30096362.373861298</v>
+        <v>35912984.6321565</v>
       </c>
       <c r="F50">
-        <v>129369590.75746164</v>
+        <v>32207141.09499783</v>
       </c>
       <c r="G50">
-        <v>269009117.4175314</v>
+        <v>138442799.5373424</v>
+      </c>
+      <c r="H50">
+        <v>287875806.8128516</v>
       </c>
     </row>
     <row r="51">
@@ -1004,22 +1062,25 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>10425688</v>
+        <v>6305009</v>
       </c>
       <c r="C52">
-        <v>2197411</v>
+        <v>11156883.35544671</v>
       </c>
       <c r="D52">
-        <v>6740508.1683287695</v>
+        <v>2351524</v>
       </c>
       <c r="E52">
-        <v>11892241.198075056</v>
+        <v>7213247.067289932</v>
       </c>
       <c r="F52">
-        <v>6385278.230397777</v>
+        <v>12726291.817073485</v>
       </c>
       <c r="G52">
-        <v>7578179.727335904</v>
+        <v>6833103.427670306</v>
+      </c>
+      <c r="H52">
+        <v>8109667.89573001</v>
       </c>
     </row>
     <row r="53">
@@ -1032,22 +1093,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>17527833</v>
+        <v>11413837</v>
       </c>
       <c r="C54">
-        <v>13802722</v>
+        <v>18757130.297276262</v>
       </c>
       <c r="D54">
-        <v>10275330.841020187</v>
+        <v>14770763</v>
       </c>
       <c r="E54">
-        <v>12959550.440209797</v>
+        <v>10995981.045268798</v>
       </c>
       <c r="F54">
-        <v>10527847.949804291</v>
+        <v>13868455.741285251</v>
       </c>
       <c r="G54">
-        <v>9635715.991862724</v>
+        <v>11266208.192672297</v>
+      </c>
+      <c r="H54">
+        <v>10311507.438878365</v>
       </c>
     </row>
     <row r="55">
@@ -1060,22 +1124,25 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
       </c>
       <c r="B56">
-        <v>79823226</v>
+        <v>104931891</v>
       </c>
       <c r="C56">
-        <v>58807181</v>
+        <v>85421549.30566318</v>
       </c>
       <c r="D56">
-        <v>92597356.37133303</v>
+        <v>62931565</v>
       </c>
       <c r="E56">
-        <v>23434880.514316123</v>
+        <v>99091580.72423545</v>
       </c>
       <c r="F56">
-        <v>37270740.24591205</v>
+        <v>25078462.76879338</v>
       </c>
       <c r="G56">
-        <v>50603207.44718195</v>
+        <v>39884686.890188344</v>
+      </c>
+      <c r="H56">
+        <v>54152213.542135656</v>
       </c>
     </row>
     <row r="57">
@@ -1098,22 +1165,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
-        <v>14937034</v>
+        <v>18808105</v>
       </c>
       <c r="C60">
-        <v>12874615</v>
+        <v>15984628.162126238</v>
       </c>
       <c r="D60">
-        <v>7140207.878505117</v>
+        <v>13777562</v>
       </c>
       <c r="E60">
-        <v>6922137.728162966</v>
+        <v>7640979.322815262</v>
       </c>
       <c r="F60">
-        <v>8620633.869815456</v>
+        <v>7407615.037343443</v>
       </c>
       <c r="G60">
-        <v>8245710.913828024</v>
+        <v>9225233.532362008</v>
+      </c>
+      <c r="H60">
+        <v>8824015.724268092</v>
       </c>
     </row>
     <row r="61">
@@ -1126,22 +1196,25 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>34183012</v>
+        <v>37696087</v>
       </c>
       <c r="C62">
-        <v>85848882</v>
+        <v>36580403.86608875</v>
       </c>
       <c r="D62">
-        <v>33821771.50691668</v>
+        <v>91869809</v>
       </c>
       <c r="E62">
-        <v>89877075.90407158</v>
+        <v>36193828.12695339</v>
       </c>
       <c r="F62">
-        <v>65118381.11277553</v>
+        <v>96180516.06669572</v>
       </c>
       <c r="G62">
-        <v>63537015.341468625</v>
+        <v>69685394.61096099</v>
+      </c>
+      <c r="H62">
+        <v>67993121.30940361</v>
       </c>
     </row>
     <row r="63">
@@ -1149,22 +1222,25 @@
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B63">
-        <v>16669183</v>
+        <v>6160092</v>
       </c>
       <c r="C63">
-        <v>14720884</v>
+        <v>17838259.725554347</v>
       </c>
       <c r="D63">
-        <v>3022909.8512303918</v>
+        <v>15753320</v>
       </c>
       <c r="E63">
-        <v>8343358.104847362</v>
+        <v>3234918.6551725166</v>
       </c>
       <c r="F63">
-        <v>6174275.046376536</v>
+        <v>8928511.304817766</v>
       </c>
       <c r="G63">
-        <v>7215400.550341232</v>
+        <v>6607301.7432392305</v>
+      </c>
+      <c r="H63">
+        <v>7721445.558603241</v>
       </c>
     </row>
     <row r="64">
@@ -1182,22 +1258,25 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>197361246</v>
+        <v>217464196</v>
       </c>
       <c r="C66">
-        <v>212765392</v>
+        <v>211202982.52811933</v>
       </c>
       <c r="D66">
-        <v>187157418.4379993</v>
+        <v>227687484</v>
       </c>
       <c r="E66">
-        <v>183525606.26354417</v>
+        <v>200283519.57389185</v>
       </c>
       <c r="F66">
-        <v>263466747.21254328</v>
+        <v>196396993.83100685</v>
       </c>
       <c r="G66">
-        <v>415824347.3895498</v>
+        <v>281944727.93443555</v>
+      </c>
+      <c r="H66">
+        <v>444987778.28187054</v>
       </c>
     </row>
     <row r="67">
@@ -1210,22 +1289,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
-        <v>20779436</v>
+        <v>15157906</v>
       </c>
       <c r="C68">
-        <v>21004985</v>
+        <v>22236781.269875918</v>
       </c>
       <c r="D68">
-        <v>26924447.246702027</v>
+        <v>22478149</v>
       </c>
       <c r="E68">
-        <v>26746171.484499995</v>
+        <v>28812766.8256841</v>
       </c>
       <c r="F68">
-        <v>20318991.68094749</v>
+        <v>28621987.868555184</v>
       </c>
       <c r="G68">
-        <v>63241523.60939885</v>
+        <v>21744044.142182577</v>
+      </c>
+      <c r="H68">
+        <v>67676905.5558532</v>
       </c>
     </row>
     <row r="69">
@@ -1252,8 +1334,8 @@
       <c r="A73" t="str">
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
-      <c r="G73">
-        <v>131925013.92225634</v>
+      <c r="H73">
+        <v>141177444.7879408</v>
       </c>
     </row>
     <row r="74">
@@ -1286,19 +1368,22 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B79">
-        <v>2871134</v>
+        <v>4567934</v>
       </c>
       <c r="C79">
+        <v>3072498.15416087</v>
+      </c>
+      <c r="D79">
         <v>0</v>
       </c>
-      <c r="D79">
-        <v>946157.1330236812</v>
-      </c>
-      <c r="F79">
-        <v>3436603.328858821</v>
+      <c r="E79">
+        <v>1012514.9312994103</v>
       </c>
       <c r="G79">
-        <v>23117704.97918758</v>
+        <v>3677626.117242117</v>
+      </c>
+      <c r="H79">
+        <v>24739042.440021746</v>
       </c>
     </row>
     <row r="80">
@@ -1306,22 +1391,25 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>20766811</v>
+        <v>19979590</v>
       </c>
       <c r="C80">
-        <v>20114690</v>
+        <v>22223270.827940334</v>
       </c>
       <c r="D80">
-        <v>16671869.77087924</v>
+        <v>21525414</v>
       </c>
       <c r="E80">
-        <v>14483458.90056832</v>
+        <v>17841134.930461925</v>
       </c>
       <c r="F80">
-        <v>11249190.718670001</v>
+        <v>15499242.020003589</v>
       </c>
       <c r="G80">
-        <v>27855974.42753963</v>
+        <v>12038141.625893172</v>
+      </c>
+      <c r="H80">
+        <v>29809625.74751576</v>
       </c>
     </row>
     <row r="81">
@@ -1344,22 +1432,25 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>44417381</v>
+        <v>39705430</v>
       </c>
       <c r="C84">
-        <v>41119675</v>
+        <v>47532550.25197712</v>
       </c>
       <c r="D84">
-        <v>44542474.15060495</v>
+        <v>44003563</v>
       </c>
       <c r="E84">
-        <v>41229630.38506831</v>
+        <v>47666416.68744543</v>
       </c>
       <c r="F84">
-        <v>35004785.72847631</v>
+        <v>44121229.888558775</v>
       </c>
       <c r="G84">
-        <v>246140216.9383824</v>
+        <v>37459811.88531786</v>
+      </c>
+      <c r="H84">
+        <v>263403018.5313315</v>
       </c>
     </row>
     <row r="85">
@@ -1372,22 +1463,25 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>3756403776</v>
+        <v>3562547307</v>
       </c>
       <c r="C86">
-        <v>3000707275</v>
+        <v>4019855453.644073</v>
       </c>
       <c r="D86">
-        <v>2606051089.2819777</v>
+        <v>3211158922</v>
       </c>
       <c r="E86">
-        <v>2269799230.2636976</v>
+        <v>2788823914.6859045</v>
       </c>
       <c r="F86">
-        <v>1623785261.4013755</v>
+        <v>2428989362.844428</v>
       </c>
       <c r="G86">
-        <v>1319889729.9564152</v>
+        <v>1737667840.7936904</v>
+      </c>
+      <c r="H86">
+        <v>1412458895.6791897</v>
       </c>
     </row>
     <row r="87">
@@ -1398,7 +1492,7 @@
         <v>137000000</v>
       </c>
       <c r="C87">
-        <v>125000000</v>
+        <v>137000000</v>
       </c>
       <c r="D87">
         <v>125000000</v>
@@ -1407,9 +1501,12 @@
         <v>125000000</v>
       </c>
       <c r="F87">
+        <v>125000000</v>
+      </c>
+      <c r="G87">
         <v>50000000</v>
       </c>
-      <c r="G87">
+      <c r="H87">
         <v>50000000</v>
       </c>
     </row>
@@ -1418,22 +1515,25 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>266497374</v>
+        <v>294796264</v>
       </c>
       <c r="C88">
-        <v>266264242</v>
+        <v>294796264.759415</v>
       </c>
       <c r="D88">
-        <v>266264241.66290888</v>
+        <v>293705174</v>
       </c>
       <c r="E88">
-        <v>266264242.18277285</v>
+        <v>293705173.7391707</v>
       </c>
       <c r="F88">
-        <v>341264241.66290885</v>
+        <v>293705174.2954948</v>
       </c>
       <c r="G88">
-        <v>341264241.66290885</v>
+        <v>368705173.7391706</v>
+      </c>
+      <c r="H88">
+        <v>368705173.7391706</v>
       </c>
     </row>
     <row r="89">
@@ -1468,6 +1568,9 @@
       <c r="B94">
         <v>512969947</v>
       </c>
+      <c r="C94">
+        <v>548946588.8034133</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -1484,22 +1587,25 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>-36825028</v>
+        <v>-37470677</v>
       </c>
       <c r="C97">
-        <v>-34952348</v>
+        <v>-39407715.05506965</v>
       </c>
       <c r="D97">
-        <v>-31067038.78471855</v>
+        <v>-37403696</v>
       </c>
       <c r="E97">
-        <v>-30125375.000993207</v>
+        <v>-33245894.939522814</v>
       </c>
       <c r="F97">
-        <v>-26207573.84784481</v>
+        <v>-32238188.494147483</v>
       </c>
       <c r="G97">
-        <v>-23957598.59137211</v>
+        <v>-28045616.21733359</v>
+      </c>
+      <c r="H97">
+        <v>-25637841.163149424</v>
       </c>
     </row>
     <row r="98">
@@ -1507,13 +1613,16 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B98">
-        <v>-3056178</v>
+        <v>-3622615</v>
       </c>
       <c r="C98">
-        <v>-1542505</v>
-      </c>
-      <c r="E98">
-        <v>39439.12597791039</v>
+        <v>-3270520.032776965</v>
+      </c>
+      <c r="D98">
+        <v>-1650688</v>
+      </c>
+      <c r="F98">
+        <v>42205.15021898932</v>
       </c>
     </row>
     <row r="99">
@@ -1521,30 +1630,33 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>104646036</v>
+        <v>182387682</v>
       </c>
       <c r="C99">
-        <v>104646036</v>
+        <v>111985282.62709157</v>
       </c>
       <c r="D99">
-        <v>104646036.08149154</v>
+        <v>111985284</v>
       </c>
       <c r="E99">
-        <v>68554413.68294217</v>
+        <v>111985282.71429844</v>
       </c>
       <c r="F99">
-        <v>65986496.52283485</v>
+        <v>73362409.93991241</v>
       </c>
       <c r="G99">
-        <v>65986496.52283485</v>
+        <v>70614394.43995047</v>
+      </c>
+      <c r="H99">
+        <v>70614394.43995047</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="D100">
-        <v>-1632037.7705347436</v>
+      <c r="E100">
+        <v>-1746499.1315239277</v>
       </c>
     </row>
     <row r="101">
@@ -1562,22 +1674,25 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>2541291850</v>
+        <v>2032817487</v>
       </c>
       <c r="C103">
-        <v>1585944791</v>
+        <v>2719522849.964182</v>
       </c>
       <c r="D103">
-        <v>1585944793.6108658</v>
+        <v>1697173468</v>
       </c>
       <c r="E103">
-        <v>1171233549.8344162</v>
+        <v>1697173469.0789168</v>
       </c>
       <c r="F103">
-        <v>886596590.3620434</v>
+        <v>1253376860.83531</v>
       </c>
       <c r="G103">
-        <v>570713251.9805062</v>
+        <v>948777168.6632178</v>
+      </c>
+      <c r="H103">
+        <v>610739663.5842328</v>
       </c>
     </row>
     <row r="104">
@@ -1585,22 +1700,25 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>233879775</v>
+        <v>443669219</v>
       </c>
       <c r="C104">
-        <v>955347059</v>
+        <v>250282702.57781753</v>
       </c>
       <c r="D104">
-        <v>556895094.4819643</v>
+        <v>1022349380</v>
       </c>
       <c r="E104">
-        <v>668832960.438582</v>
+        <v>595952383.2245651</v>
       </c>
       <c r="F104">
-        <v>306145506.7014332</v>
+        <v>715740901.1176397</v>
       </c>
       <c r="G104">
-        <v>315883338.38153726</v>
+        <v>327616720.16868514</v>
+      </c>
+      <c r="H104">
+        <v>338037505.07898504</v>
       </c>
     </row>
     <row r="105">
@@ -1613,22 +1731,25 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>3756403776</v>
+        <v>3562547307</v>
       </c>
       <c r="C106">
-        <v>3000707275</v>
+        <v>4019855453.644073</v>
       </c>
       <c r="D106">
-        <v>2606051089.2819777</v>
+        <v>3211158922</v>
       </c>
       <c r="E106">
-        <v>2269799230.2636976</v>
+        <v>2788823914.6859045</v>
       </c>
       <c r="F106">
-        <v>1623785261.4013755</v>
+        <v>2428989362.844428</v>
       </c>
       <c r="G106">
-        <v>1319889729.9564152</v>
+        <v>1737667840.7936904</v>
+      </c>
+      <c r="H106">
+        <v>1412458895.6791897</v>
       </c>
     </row>
     <row r="107">
@@ -1636,22 +1757,25 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>3998182403</v>
+        <v>3819716933</v>
       </c>
       <c r="C107">
-        <v>3254592342</v>
+        <v>4278590986.424169</v>
       </c>
       <c r="D107">
-        <v>2837750981.8705816</v>
+        <v>3482849969</v>
       </c>
       <c r="E107">
-        <v>2494554466.91231</v>
+        <v>3036773850.947242</v>
       </c>
       <c r="F107">
-        <v>1922256794.342395</v>
+        <v>2669507586.5639935</v>
       </c>
       <c r="G107">
-        <v>1981854294.2843473</v>
+        <v>2057072380.6134439</v>
+      </c>
+      <c r="H107">
+        <v>2120849692.4923916</v>
       </c>
     </row>
     <row r="108">
@@ -1659,19 +1783,22 @@
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
       <c r="C108">
+        <v>1576115.8496640583</v>
+      </c>
+      <c r="D108">
         <v>6399355</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1682,6 +1809,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1689,27 +1818,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1723,28 +1858,34 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>473649872</v>
+        <v>917070900</v>
       </c>
       <c r="C3">
-        <v>1545478883.7027836</v>
+        <v>506868839</v>
       </c>
       <c r="D3">
-        <v>1033474250.2673897</v>
+        <v>1653869522.4505036</v>
       </c>
       <c r="E3">
-        <v>411575792</v>
+        <v>1105955948.5274262</v>
       </c>
       <c r="F3">
-        <v>1292532946.0532973</v>
+        <v>788621229</v>
       </c>
       <c r="G3">
-        <v>812728170.3518273</v>
+        <v>440441254</v>
       </c>
       <c r="H3">
-        <v>1019558119.1714649</v>
+        <v>1383183470.6916733</v>
       </c>
       <c r="I3">
-        <v>926002874.1450098</v>
+        <v>869728059.79816</v>
+      </c>
+      <c r="J3">
+        <v>1091063823.2886567</v>
+      </c>
+      <c r="K3">
+        <v>990947173.33228</v>
       </c>
     </row>
     <row r="4">
@@ -1767,28 +1908,34 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-24898570</v>
+        <v>-53392524</v>
       </c>
       <c r="C7">
-        <v>-136272000.4199814</v>
+        <v>-26644807</v>
       </c>
       <c r="D7">
-        <v>-73770136.35890141</v>
+        <v>-145829302.9005968</v>
       </c>
       <c r="E7">
-        <v>-26407918</v>
+        <v>-78943932.18669705</v>
       </c>
       <c r="F7">
-        <v>-114145495.30322978</v>
+        <v>-48694106</v>
       </c>
       <c r="G7">
-        <v>-63423216.361740544</v>
+        <v>-28260011</v>
       </c>
       <c r="H7">
-        <v>-105772362.10919988</v>
+        <v>-122150977.14873347</v>
       </c>
       <c r="I7">
-        <v>-140369092.74821365</v>
+        <v>-67871341.15035847</v>
+      </c>
+      <c r="J7">
+        <v>-113190602.50819075</v>
+      </c>
+      <c r="K7">
+        <v>-150213740.76240343</v>
       </c>
     </row>
     <row r="8">
@@ -1796,28 +1943,34 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>448751302</v>
+        <v>863678376</v>
       </c>
       <c r="C8">
-        <v>1409206883.282802</v>
+        <v>480224032</v>
       </c>
       <c r="D8">
-        <v>959704113.9084883</v>
+        <v>1508040219.5499067</v>
       </c>
       <c r="E8">
-        <v>385167874</v>
+        <v>1027012016.3407292</v>
       </c>
       <c r="F8">
-        <v>1178387450.7500675</v>
+        <v>739927123</v>
       </c>
       <c r="G8">
-        <v>749304953.9900867</v>
+        <v>412181243</v>
       </c>
       <c r="H8">
-        <v>913785757.062265</v>
+        <v>1261032493.54294</v>
       </c>
       <c r="I8">
-        <v>785633781.3967962</v>
+        <v>801856718.6478014</v>
+      </c>
+      <c r="J8">
+        <v>977873220.780466</v>
+      </c>
+      <c r="K8">
+        <v>840733432.5698768</v>
       </c>
     </row>
     <row r="9">
@@ -1845,28 +1998,34 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>448751302</v>
+        <v>863678376</v>
       </c>
       <c r="C13">
-        <v>1409206883.282802</v>
+        <v>480224032</v>
       </c>
       <c r="D13">
-        <v>959704113.9084883</v>
+        <v>1508040219.5499067</v>
       </c>
       <c r="E13">
-        <v>385167874</v>
+        <v>1027012016.3407292</v>
       </c>
       <c r="F13">
-        <v>1178387450.7500675</v>
+        <v>739927123</v>
       </c>
       <c r="G13">
-        <v>749304953.9900867</v>
+        <v>412181243</v>
       </c>
       <c r="H13">
-        <v>913785757.062265</v>
+        <v>1261032493.54294</v>
       </c>
       <c r="I13">
-        <v>785633781.3967962</v>
+        <v>801856718.6478014</v>
+      </c>
+      <c r="J13">
+        <v>977873220.780466</v>
+      </c>
+      <c r="K13">
+        <v>840733432.5698768</v>
       </c>
     </row>
     <row r="14"/>
@@ -1875,28 +2034,34 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-111100769</v>
+        <v>-211477915</v>
       </c>
       <c r="C15">
-        <v>-230860795.19644153</v>
+        <v>-118892712</v>
       </c>
       <c r="D15">
-        <v>-166362043.81947124</v>
+        <v>-247051989.60033813</v>
       </c>
       <c r="E15">
-        <v>-55731821</v>
+        <v>-178029681.84618172</v>
       </c>
       <c r="F15">
-        <v>-215866146.24057806</v>
+        <v>-124642152</v>
       </c>
       <c r="G15">
-        <v>-150554060.09335297</v>
+        <v>-59640517</v>
       </c>
       <c r="H15">
-        <v>-212991312.99062726</v>
+        <v>-231005705.71418697</v>
       </c>
       <c r="I15">
-        <v>-244781095.5286438</v>
+        <v>-161113020.7570429</v>
+      </c>
+      <c r="J15">
+        <v>-227929248.86682487</v>
+      </c>
+      <c r="K15">
+        <v>-261948576.4806636</v>
       </c>
     </row>
     <row r="16">
@@ -1904,28 +2069,34 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-1994930</v>
+        <v>-4194510</v>
       </c>
       <c r="C16">
-        <v>-10681544.763050426</v>
+        <v>-2134842</v>
       </c>
       <c r="D16">
-        <v>-6901377.928285054</v>
+        <v>-11430684.380477937</v>
       </c>
       <c r="E16">
-        <v>-1663836</v>
+        <v>-7385399.26935573</v>
       </c>
       <c r="F16">
-        <v>-11375884.661293674</v>
+        <v>-4600860</v>
       </c>
       <c r="G16">
-        <v>-6703534.8111439105</v>
+        <v>-1780528</v>
       </c>
       <c r="H16">
-        <v>-13865122.630763656</v>
+        <v>-12173721.123351179</v>
       </c>
       <c r="I16">
-        <v>-18376634.710318897</v>
+        <v>-7173680.620128771</v>
+      </c>
+      <c r="J16">
+        <v>-14837539.345163073</v>
+      </c>
+      <c r="K16">
+        <v>-19665461.879223812</v>
       </c>
     </row>
     <row r="17">
@@ -1933,28 +2104,34 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
-        <v>-63890536</v>
+        <v>-176559398</v>
       </c>
       <c r="C17">
-        <v>-175537312.53554627</v>
+        <v>-68371436</v>
       </c>
       <c r="D17">
-        <v>-170092068.40914464</v>
+        <v>-187848448.99326387</v>
       </c>
       <c r="E17">
-        <v>-35706361</v>
+        <v>-182021308.0352576</v>
       </c>
       <c r="F17">
-        <v>-155590032.61095032</v>
+        <v>-102214735</v>
       </c>
       <c r="G17">
-        <v>-128073308.09290156</v>
+        <v>-38210592</v>
       </c>
       <c r="H17">
-        <v>-173263976.39978975</v>
+        <v>-166502186.24521685</v>
       </c>
       <c r="I17">
-        <v>-168924846.2678411</v>
+        <v>-137055603.36533105</v>
+      </c>
+      <c r="J17">
+        <v>-185415674.66754478</v>
+      </c>
+      <c r="K17">
+        <v>-180772223.91913804</v>
       </c>
     </row>
     <row r="18">
@@ -1962,28 +2139,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>8498506</v>
+        <v>27997686</v>
       </c>
       <c r="C18">
-        <v>92090973.19392009</v>
+        <v>9094540</v>
       </c>
       <c r="D18">
-        <v>63453804.904627554</v>
+        <v>98549682.86161412</v>
       </c>
       <c r="E18">
-        <v>26274663</v>
+        <v>67904074.99056195</v>
       </c>
       <c r="F18">
-        <v>55731387.10334759</v>
+        <v>52705921</v>
       </c>
       <c r="G18">
-        <v>40809633.8118923</v>
+        <v>28117412</v>
       </c>
       <c r="H18">
-        <v>41260020.44981914</v>
+        <v>59640053.02568963</v>
       </c>
       <c r="I18">
-        <v>40906417.72085577</v>
+        <v>43671777.2695458</v>
+      </c>
+      <c r="J18">
+        <v>44153751.33055756</v>
+      </c>
+      <c r="K18">
+        <v>43775349.022603214</v>
       </c>
     </row>
     <row r="19">
@@ -1991,28 +2174,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-16777365</v>
+        <v>-26973099</v>
       </c>
       <c r="C19">
-        <v>-21709138.145161886</v>
+        <v>-17954029</v>
       </c>
       <c r="D19">
-        <v>-16045247.32980916</v>
+        <v>-23231687.15895295</v>
       </c>
       <c r="E19">
-        <v>-6294611</v>
+        <v>-17170564.941898663</v>
       </c>
       <c r="F19">
-        <v>-65249955.2332158</v>
+        <v>-16053028</v>
       </c>
       <c r="G19">
-        <v>-29781524.178372663</v>
+        <v>-6736078</v>
       </c>
       <c r="H19">
-        <v>-98931590.53778487</v>
+        <v>-69826196.55269831</v>
       </c>
       <c r="I19">
-        <v>-39178034.71025356</v>
+        <v>-31870222.032878757</v>
+      </c>
+      <c r="J19">
+        <v>-105870060.1628287</v>
+      </c>
+      <c r="K19">
+        <v>-41925747.572528675</v>
       </c>
     </row>
     <row r="20">
@@ -2025,28 +2214,34 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>263486208</v>
+        <v>472471140</v>
       </c>
       <c r="C21">
-        <v>1062509065.8365221</v>
+        <v>281965553</v>
       </c>
       <c r="D21">
-        <v>663757181.3264056</v>
+        <v>1137027092.278488</v>
       </c>
       <c r="E21">
-        <v>312045908</v>
+        <v>710309137.2385974</v>
       </c>
       <c r="F21">
-        <v>786036819.1073773</v>
+        <v>545122269</v>
       </c>
       <c r="G21">
-        <v>475002160.62620795</v>
+        <v>333930940</v>
       </c>
       <c r="H21">
-        <v>455993774.95311856</v>
+        <v>841164736.9331763</v>
       </c>
       <c r="I21">
-        <v>355279587.9005946</v>
+        <v>508315969.1419658</v>
+      </c>
+      <c r="J21">
+        <v>487974449.068662</v>
+      </c>
+      <c r="K21">
+        <v>380196771.74092585</v>
       </c>
     </row>
     <row r="22"/>
@@ -2065,28 +2260,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>70877540</v>
+        <v>154727732</v>
       </c>
       <c r="C25">
-        <v>44868504.89245191</v>
+        <v>75848466</v>
       </c>
       <c r="D25">
-        <v>13000416.665605454</v>
+        <v>48015313.27413365</v>
       </c>
       <c r="E25">
-        <v>174993</v>
+        <v>13912188.07913353</v>
       </c>
       <c r="F25">
-        <v>52816.95674000461</v>
+        <v>189275</v>
       </c>
       <c r="G25">
-        <v>52817.11309626338</v>
+        <v>187266</v>
       </c>
       <c r="H25">
-        <v>37247.812331834575</v>
+        <v>56521.22196040264</v>
       </c>
       <c r="I25">
-        <v>11870266.6394058</v>
+        <v>56521.389282553566</v>
+      </c>
+      <c r="J25">
+        <v>39860.150949447925</v>
+      </c>
+      <c r="K25">
+        <v>12702776.094383499</v>
       </c>
     </row>
     <row r="26">
@@ -2097,22 +2298,28 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>-6821.5162370833295</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>-6821.186498060714</v>
+        <v>-7299.93655712932</v>
       </c>
       <c r="E26">
-        <v>-6821</v>
+        <v>-7299.583692185245</v>
       </c>
       <c r="F26">
+        <v>-7299</v>
+      </c>
+      <c r="G26">
+        <v>-7299</v>
+      </c>
+      <c r="H26">
         <v>0</v>
       </c>
-      <c r="H26">
-        <v>-45738000.77083173</v>
-      </c>
-      <c r="I26">
-        <v>-10342.021145039527</v>
+      <c r="J26">
+        <v>-48945790.389229104</v>
+      </c>
+      <c r="K26">
+        <v>-11067.348608050559</v>
       </c>
     </row>
     <row r="27">
@@ -2150,28 +2357,34 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>334363748</v>
+        <v>627198872</v>
       </c>
       <c r="C33">
-        <v>1107370749.2127368</v>
+        <v>357814019</v>
       </c>
       <c r="D33">
-        <v>676750776.8055131</v>
+        <v>1185035105.6160643</v>
       </c>
       <c r="E33">
-        <v>312214080</v>
+        <v>724214025.7340388</v>
       </c>
       <c r="F33">
-        <v>786089636.0641173</v>
+        <v>545304245</v>
       </c>
       <c r="G33">
-        <v>475054977.73930424</v>
+        <v>334110907</v>
       </c>
       <c r="H33">
-        <v>410293021.9946187</v>
+        <v>841221258.1551367</v>
       </c>
       <c r="I33">
-        <v>367139512.5188553</v>
+        <v>508372490.5312484</v>
+      </c>
+      <c r="J33">
+        <v>439068518.8303824</v>
+      </c>
+      <c r="K33">
+        <v>392888480.4867012</v>
       </c>
     </row>
     <row r="34"/>
@@ -2180,28 +2393,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>2912197</v>
+        <v>5098576</v>
       </c>
       <c r="C35">
-        <v>54710264.775151044</v>
+        <v>3116441</v>
       </c>
       <c r="D35">
-        <v>53244019.46477509</v>
+        <v>58547315.289117135</v>
       </c>
       <c r="E35">
-        <v>16987092</v>
+        <v>56978236.308589876</v>
       </c>
       <c r="F35">
-        <v>20151619.49438084</v>
+        <v>45861936</v>
       </c>
       <c r="G35">
-        <v>12091982.760942262</v>
+        <v>18178465</v>
       </c>
       <c r="H35">
-        <v>8661908.938216096</v>
+        <v>21564933.472222935</v>
       </c>
       <c r="I35">
-        <v>3207269.0673849643</v>
+        <v>12940042.057646964</v>
+      </c>
+      <c r="J35">
+        <v>9269403.38701659</v>
+      </c>
+      <c r="K35">
+        <v>3432207.723302903</v>
       </c>
     </row>
     <row r="36">
@@ -2209,28 +2428,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-4774664</v>
+        <v>-10344741</v>
       </c>
       <c r="C36">
-        <v>-16854915.718782995</v>
+        <v>-5109530</v>
       </c>
       <c r="D36">
-        <v>-11670993.829135014</v>
+        <v>-18037018.625566687</v>
       </c>
       <c r="E36">
-        <v>-3547760</v>
+        <v>-12489527.481907926</v>
       </c>
       <c r="F36">
-        <v>-17701662.96939272</v>
+        <v>-7825887</v>
       </c>
       <c r="G36">
-        <v>-12873277.328377713</v>
+        <v>-3796578</v>
       </c>
       <c r="H36">
-        <v>-76131812.56349748</v>
+        <v>-18943151.660297625</v>
       </c>
       <c r="I36">
-        <v>-127430875.19800904</v>
+        <v>-13776131.949759744</v>
+      </c>
+      <c r="J36">
+        <v>-81471242.22494225</v>
+      </c>
+      <c r="K36">
+        <v>-136368114.07234457</v>
       </c>
     </row>
     <row r="37">
@@ -2238,28 +2463,34 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-98621506</v>
+        <v>-178283488</v>
       </c>
       <c r="C37">
-        <v>-189879041.47881964</v>
+        <v>-105538228</v>
       </c>
       <c r="D37">
-        <v>-161428707.95918888</v>
+        <v>-203196020.96506417</v>
       </c>
       <c r="E37">
-        <v>-62664977</v>
+        <v>-172750351.33615565</v>
       </c>
       <c r="F37">
-        <v>-119706632.1505235</v>
+        <v>-111219931</v>
       </c>
       <c r="G37">
-        <v>-97444436.37615599</v>
+        <v>-67059923</v>
       </c>
       <c r="H37">
-        <v>-36677611.66790409</v>
+        <v>-128102138.84942245</v>
       </c>
       <c r="I37">
-        <v>63869979.962057725</v>
+        <v>-104278605.90936737</v>
+      </c>
+      <c r="J37">
+        <v>-39249959.823771544</v>
+      </c>
+      <c r="K37">
+        <v>68349438.07558759</v>
       </c>
     </row>
     <row r="38">
@@ -2267,28 +2498,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>233879775</v>
+        <v>443669219</v>
       </c>
       <c r="C38">
-        <v>955347056.7902853</v>
+        <v>250282702</v>
       </c>
       <c r="D38">
-        <v>556895094.4819643</v>
+        <v>1022349381.3145508</v>
       </c>
       <c r="E38">
-        <v>262988435</v>
+        <v>595952383.2245651</v>
       </c>
       <c r="F38">
-        <v>668832960.438582</v>
+        <v>472120363</v>
       </c>
       <c r="G38">
-        <v>376829246.79571277</v>
+        <v>281432871</v>
       </c>
       <c r="H38">
-        <v>306145506.7014332</v>
+        <v>715740901.1176397</v>
       </c>
       <c r="I38">
-        <v>306785886.350289</v>
+        <v>403257794.7297682</v>
+      </c>
+      <c r="J38">
+        <v>327616720.16868514</v>
+      </c>
+      <c r="K38">
+        <v>328302012.2132472</v>
       </c>
     </row>
     <row r="39"/>
@@ -2296,8 +2533,8 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
-      <c r="I40">
-        <v>9097452.03124833</v>
+      <c r="K40">
+        <v>9735492.86573791</v>
       </c>
     </row>
     <row r="41">
@@ -2315,28 +2552,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>233879775</v>
+        <v>443669219</v>
       </c>
       <c r="C43">
-        <v>955347056.7902853</v>
+        <v>250282702</v>
       </c>
       <c r="D43">
-        <v>556895094.4819643</v>
+        <v>1022349381.3145508</v>
       </c>
       <c r="E43">
-        <v>262988435</v>
+        <v>595952383.2245651</v>
       </c>
       <c r="F43">
-        <v>668832960.438582</v>
+        <v>472120363</v>
       </c>
       <c r="G43">
-        <v>376829246.79571277</v>
+        <v>281432871</v>
       </c>
       <c r="H43">
-        <v>306145506.7014332</v>
+        <v>715740901.1176397</v>
       </c>
       <c r="I43">
-        <v>315883338.38153726</v>
+        <v>403257794.7297682</v>
+      </c>
+      <c r="J43">
+        <v>327616720.16868514</v>
+      </c>
+      <c r="K43">
+        <v>338037505.07898504</v>
       </c>
     </row>
     <row r="44">
@@ -2350,28 +2593,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>233879775</v>
+        <v>443669219</v>
       </c>
       <c r="C46">
-        <v>955347056.7902853</v>
+        <v>250282702</v>
       </c>
       <c r="D46">
-        <v>556895094.4819643</v>
+        <v>1022349381.3145508</v>
       </c>
       <c r="E46">
-        <v>262988435</v>
+        <v>595952383.2245651</v>
       </c>
       <c r="F46">
-        <v>668832960.438582</v>
+        <v>472120363</v>
       </c>
       <c r="G46">
-        <v>376829246.79571277</v>
+        <v>281432871</v>
       </c>
       <c r="H46">
-        <v>306145506.7014332</v>
+        <v>715740901.1176397</v>
       </c>
       <c r="I46">
-        <v>315883338.38153726</v>
+        <v>403257794.7297682</v>
+      </c>
+      <c r="J46">
+        <v>327616720.16868514</v>
+      </c>
+      <c r="K46">
+        <v>338037505.07898504</v>
       </c>
     </row>
     <row r="47">
@@ -2384,10 +2633,16 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="D47">
         <v>0</v>
       </c>
       <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -2396,28 +2651,34 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>233879775</v>
+        <v>443669219</v>
       </c>
       <c r="C48">
-        <v>955347056.7902853</v>
+        <v>250282702</v>
       </c>
       <c r="D48">
-        <v>556895094.4819643</v>
+        <v>1022349381.3145508</v>
       </c>
       <c r="E48">
-        <v>262988435</v>
+        <v>595952383.2245651</v>
       </c>
       <c r="F48">
-        <v>668832960.438582</v>
+        <v>472120363</v>
       </c>
       <c r="G48">
-        <v>376829246.79571277</v>
+        <v>281432871</v>
       </c>
       <c r="H48">
-        <v>306145506.7014332</v>
+        <v>715740901.1176397</v>
       </c>
       <c r="I48">
-        <v>315883338.38153726</v>
+        <v>403257794.7297682</v>
+      </c>
+      <c r="J48">
+        <v>327616720.16868514</v>
+      </c>
+      <c r="K48">
+        <v>338037505.07898504</v>
       </c>
     </row>
     <row r="49"/>
@@ -2426,40 +2687,46 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>82636625</v>
+        <v>215214529</v>
       </c>
       <c r="C50">
-        <v>249292175.53229913</v>
+        <v>88432263.27248536</v>
       </c>
       <c r="D50">
-        <v>222763720.27751082</v>
+        <v>266776036.6356069</v>
       </c>
       <c r="E50">
-        <v>53093035</v>
+        <v>238387034.3100184</v>
       </c>
       <c r="F50">
-        <v>216135364.49310306</v>
+        <v>141587906</v>
       </c>
       <c r="G50">
-        <v>173303889.52758655</v>
+        <v>56816662.69714282</v>
       </c>
       <c r="H50">
-        <v>227972426.51804158</v>
+        <v>231293805.32359198</v>
       </c>
       <c r="I50">
-        <v>250206367.5504006</v>
+        <v>185458387.0632332</v>
+      </c>
+      <c r="J50">
+        <v>243961048.03058904</v>
+      </c>
+      <c r="K50">
+        <v>267754344.6101443</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2470,6 +2737,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2477,27 +2746,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2511,16 +2786,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>473649872</v>
+        <v>410202061</v>
       </c>
       <c r="C3">
-        <v>512004633.4353939</v>
+        <v>506868839</v>
+      </c>
+      <c r="D3">
+        <v>547913573.9230773</v>
       </c>
       <c r="E3">
-        <v>411575792</v>
+        <v>317334719.52742624</v>
       </c>
       <c r="F3">
-        <v>479804775.70147</v>
+        <v>348179975</v>
+      </c>
+      <c r="G3">
+        <v>440441254</v>
+      </c>
+      <c r="H3">
+        <v>513455410.8935133</v>
       </c>
     </row>
     <row r="4">
@@ -2543,16 +2827,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-24898570</v>
+        <v>-26747717</v>
       </c>
       <c r="C7">
-        <v>-62501864.06107998</v>
+        <v>-26644807</v>
+      </c>
+      <c r="D7">
+        <v>-66885370.71389975</v>
       </c>
       <c r="E7">
-        <v>-26407918</v>
+        <v>-30249826.18669705</v>
       </c>
       <c r="F7">
-        <v>-50722278.941489235</v>
+        <v>-20434095</v>
+      </c>
+      <c r="G7">
+        <v>-28260011</v>
+      </c>
+      <c r="H7">
+        <v>-54279635.998375</v>
       </c>
     </row>
     <row r="8">
@@ -2560,16 +2853,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>448751302</v>
+        <v>383454344</v>
       </c>
       <c r="C8">
-        <v>449502769.37431383</v>
+        <v>480224032</v>
+      </c>
+      <c r="D8">
+        <v>481028203.2091775</v>
       </c>
       <c r="E8">
-        <v>385167874</v>
+        <v>287084893.34072924</v>
       </c>
       <c r="F8">
-        <v>429082496.7599808</v>
+        <v>327745880</v>
+      </c>
+      <c r="G8">
+        <v>412181243</v>
+      </c>
+      <c r="H8">
+        <v>459175774.8951385</v>
       </c>
     </row>
     <row r="9">
@@ -2597,16 +2899,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>448751302</v>
+        <v>383454344</v>
       </c>
       <c r="C13">
-        <v>449502769.37431383</v>
+        <v>480224032</v>
+      </c>
+      <c r="D13">
+        <v>481028203.2091775</v>
       </c>
       <c r="E13">
-        <v>385167874</v>
+        <v>287084893.34072924</v>
       </c>
       <c r="F13">
-        <v>429082496.7599808</v>
+        <v>327745880</v>
+      </c>
+      <c r="G13">
+        <v>412181243</v>
+      </c>
+      <c r="H13">
+        <v>459175774.8951385</v>
       </c>
     </row>
     <row r="14"/>
@@ -2615,16 +2926,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-111100769</v>
+        <v>-92585203</v>
       </c>
       <c r="C15">
-        <v>-64498751.37697029</v>
+        <v>-118892712</v>
+      </c>
+      <c r="D15">
+        <v>-69022307.75415641</v>
       </c>
       <c r="E15">
-        <v>-55731821</v>
+        <v>-53387529.84618172</v>
       </c>
       <c r="F15">
-        <v>-65312086.14722508</v>
+        <v>-65001635</v>
+      </c>
+      <c r="G15">
+        <v>-59640517</v>
+      </c>
+      <c r="H15">
+        <v>-69892684.95714405</v>
       </c>
     </row>
     <row r="16">
@@ -2632,16 +2952,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-1994930</v>
+        <v>-2059668</v>
       </c>
       <c r="C16">
-        <v>-3780166.834765372</v>
+        <v>-2134842</v>
+      </c>
+      <c r="D16">
+        <v>-4045285.111122207</v>
       </c>
       <c r="E16">
-        <v>-1663836</v>
+        <v>-2784539.26935573</v>
       </c>
       <c r="F16">
-        <v>-4672349.850149764</v>
+        <v>-2820332</v>
+      </c>
+      <c r="G16">
+        <v>-1780528</v>
+      </c>
+      <c r="H16">
+        <v>-5000040.503222408</v>
       </c>
     </row>
     <row r="17">
@@ -2649,16 +2978,25 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
-        <v>-63890536</v>
+        <v>-108187962</v>
       </c>
       <c r="C17">
-        <v>-5445244.126401633</v>
+        <v>-68371436</v>
+      </c>
+      <c r="D17">
+        <v>-5827140.958006263</v>
       </c>
       <c r="E17">
-        <v>-35706361</v>
+        <v>-79806573.03525761</v>
       </c>
       <c r="F17">
-        <v>-27516724.518048763</v>
+        <v>-64004143</v>
+      </c>
+      <c r="G17">
+        <v>-38210592</v>
+      </c>
+      <c r="H17">
+        <v>-29446582.879885793</v>
       </c>
     </row>
     <row r="18">
@@ -2666,16 +3004,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>8498506</v>
+        <v>18903146</v>
       </c>
       <c r="C18">
-        <v>28637168.289292537</v>
+        <v>9094540</v>
+      </c>
+      <c r="D18">
+        <v>30645607.871052176</v>
       </c>
       <c r="E18">
-        <v>26274663</v>
+        <v>15198153.990561947</v>
       </c>
       <c r="F18">
-        <v>14921753.291455291</v>
+        <v>24588509</v>
+      </c>
+      <c r="G18">
+        <v>28117412</v>
+      </c>
+      <c r="H18">
+        <v>15968275.75614383</v>
       </c>
     </row>
     <row r="19">
@@ -2683,16 +3030,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-16777365</v>
+        <v>-9019070</v>
       </c>
       <c r="C19">
-        <v>-5663890.815352725</v>
+        <v>-17954029</v>
+      </c>
+      <c r="D19">
+        <v>-6061122.217054289</v>
       </c>
       <c r="E19">
-        <v>-6294611</v>
+        <v>-1117536.9418986626</v>
       </c>
       <c r="F19">
-        <v>-35468431.05484314</v>
+        <v>-9316950</v>
+      </c>
+      <c r="G19">
+        <v>-6736078</v>
+      </c>
+      <c r="H19">
+        <v>-37955974.51981956</v>
       </c>
     </row>
     <row r="20">
@@ -2705,16 +3061,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>263486208</v>
+        <v>190505587</v>
       </c>
       <c r="C21">
-        <v>398751884.51011646</v>
+        <v>281965553</v>
+      </c>
+      <c r="D21">
+        <v>426717955.0398905</v>
       </c>
       <c r="E21">
-        <v>312045908</v>
+        <v>165186868.2385974</v>
       </c>
       <c r="F21">
-        <v>311034658.48116934</v>
+        <v>211191329</v>
+      </c>
+      <c r="G21">
+        <v>333930940</v>
+      </c>
+      <c r="H21">
+        <v>332848767.7912105</v>
       </c>
     </row>
     <row r="22"/>
@@ -2733,16 +3098,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>70877540</v>
+        <v>78879266</v>
       </c>
       <c r="C25">
-        <v>31868088.226846457</v>
+        <v>75848466</v>
+      </c>
+      <c r="D25">
+        <v>34103125.19500013</v>
       </c>
       <c r="E25">
-        <v>174993</v>
+        <v>13722913.07913353</v>
       </c>
       <c r="F25">
-        <v>-0.1563562587762135</v>
+        <v>2009</v>
+      </c>
+      <c r="G25">
+        <v>187266</v>
+      </c>
+      <c r="H25">
+        <v>-0.1673221509263385</v>
       </c>
     </row>
     <row r="26">
@@ -2753,10 +3127,19 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>-0.32973902261528565</v>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>-0.3528649440750087</v>
       </c>
       <c r="E26">
-        <v>-6821</v>
+        <v>-0.5836921852451269</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>-7299</v>
       </c>
     </row>
     <row r="27">
@@ -2794,16 +3177,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>334363748</v>
+        <v>269384853</v>
       </c>
       <c r="C33">
-        <v>430619972.4072237</v>
+        <v>357814019</v>
+      </c>
+      <c r="D33">
+        <v>460821079.8820255</v>
       </c>
       <c r="E33">
-        <v>312214080</v>
+        <v>178909780.73403883</v>
       </c>
       <c r="F33">
-        <v>311034658.32481307</v>
+        <v>211193338</v>
+      </c>
+      <c r="G33">
+        <v>334110907</v>
+      </c>
+      <c r="H33">
+        <v>332848767.6238883</v>
       </c>
     </row>
     <row r="34"/>
@@ -2812,16 +3204,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>2912197</v>
+        <v>1982135</v>
       </c>
       <c r="C35">
-        <v>1466245.3103759512</v>
+        <v>3116441</v>
+      </c>
+      <c r="D35">
+        <v>1569078.9805272594</v>
       </c>
       <c r="E35">
-        <v>16987092</v>
+        <v>11116300.308589876</v>
       </c>
       <c r="F35">
-        <v>8059636.7334385775</v>
+        <v>27683471</v>
+      </c>
+      <c r="G35">
+        <v>18178465</v>
+      </c>
+      <c r="H35">
+        <v>8624891.414575972</v>
       </c>
     </row>
     <row r="36">
@@ -2829,16 +3230,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-4774664</v>
+        <v>-5235211</v>
       </c>
       <c r="C36">
-        <v>-5183921.889647981</v>
+        <v>-5109530</v>
+      </c>
+      <c r="D36">
+        <v>-5547491.143658761</v>
       </c>
       <c r="E36">
-        <v>-3547760</v>
+        <v>-4663640.4819079265</v>
       </c>
       <c r="F36">
-        <v>-4828385.641015008</v>
+        <v>-4029309</v>
+      </c>
+      <c r="G36">
+        <v>-3796578</v>
+      </c>
+      <c r="H36">
+        <v>-5167019.710537881</v>
       </c>
     </row>
     <row r="37">
@@ -2846,16 +3256,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-98621506</v>
+        <v>-72745260</v>
       </c>
       <c r="C37">
-        <v>-28450333.51963076</v>
+        <v>-105538228</v>
+      </c>
+      <c r="D37">
+        <v>-30445669.628908515</v>
       </c>
       <c r="E37">
-        <v>-62664977</v>
+        <v>-61530420.33615565</v>
       </c>
       <c r="F37">
-        <v>-22262195.77436751</v>
+        <v>-44160008</v>
+      </c>
+      <c r="G37">
+        <v>-67059923</v>
+      </c>
+      <c r="H37">
+        <v>-23823532.940055087</v>
       </c>
     </row>
     <row r="38">
@@ -2863,16 +3282,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>233879775</v>
+        <v>193386517</v>
       </c>
       <c r="C38">
-        <v>398451962.308321</v>
+        <v>250282702</v>
+      </c>
+      <c r="D38">
+        <v>426396998.0899856</v>
       </c>
       <c r="E38">
-        <v>262988435</v>
+        <v>123832020.22456515</v>
       </c>
       <c r="F38">
-        <v>292003713.6428692</v>
+        <v>190687492</v>
+      </c>
+      <c r="G38">
+        <v>281432871</v>
+      </c>
+      <c r="H38">
+        <v>312483106.38787144</v>
       </c>
     </row>
     <row r="39"/>
@@ -2896,16 +3324,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>233879775</v>
+        <v>193386517</v>
       </c>
       <c r="C43">
-        <v>398451962.308321</v>
+        <v>250282702</v>
+      </c>
+      <c r="D43">
+        <v>426396998.0899856</v>
       </c>
       <c r="E43">
-        <v>262988435</v>
+        <v>123832020.22456515</v>
       </c>
       <c r="F43">
-        <v>292003713.6428692</v>
+        <v>190687492</v>
+      </c>
+      <c r="G43">
+        <v>281432871</v>
+      </c>
+      <c r="H43">
+        <v>312483106.38787144</v>
       </c>
     </row>
     <row r="44">
@@ -2919,16 +3356,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>233879775</v>
+        <v>193386517</v>
       </c>
       <c r="C46">
-        <v>398451962.308321</v>
+        <v>250282702</v>
+      </c>
+      <c r="D46">
+        <v>426396998.0899856</v>
       </c>
       <c r="E46">
-        <v>262988435</v>
+        <v>123832020.22456515</v>
       </c>
       <c r="F46">
-        <v>292003713.6428692</v>
+        <v>190687492</v>
+      </c>
+      <c r="G46">
+        <v>281432871</v>
+      </c>
+      <c r="H46">
+        <v>312483106.38787144</v>
       </c>
     </row>
     <row r="47">
@@ -2938,7 +3384,13 @@
       <c r="B47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0</v>
       </c>
     </row>
@@ -2947,16 +3399,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>233879775</v>
+        <v>193386517</v>
       </c>
       <c r="C48">
-        <v>398451962.308321</v>
+        <v>250282702</v>
+      </c>
+      <c r="D48">
+        <v>426396998.0899856</v>
       </c>
       <c r="E48">
-        <v>262988435</v>
+        <v>123832020.22456515</v>
       </c>
       <c r="F48">
-        <v>292003713.6428692</v>
+        <v>190687492</v>
+      </c>
+      <c r="G48">
+        <v>281432871</v>
+      </c>
+      <c r="H48">
+        <v>312483106.38787144</v>
       </c>
     </row>
     <row r="49"/>
@@ -2965,28 +3426,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>82636625</v>
+        <v>126782265.72751464</v>
       </c>
       <c r="C50">
-        <v>26528455.25478831</v>
+        <v>88432263.27248536</v>
+      </c>
+      <c r="D50">
+        <v>28389002.325588524</v>
       </c>
       <c r="E50">
-        <v>53093035</v>
+        <v>96799128.31001839</v>
       </c>
       <c r="F50">
-        <v>42831474.96551651</v>
+        <v>84771243.30285719</v>
+      </c>
+      <c r="G50">
+        <v>56816662.69714282</v>
+      </c>
+      <c r="H50">
+        <v>45835418.26035878</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2997,6 +3467,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3004,27 +3476,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3038,22 +3516,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1607552963.7027836</v>
+        <v>1782319193.4505036</v>
       </c>
       <c r="C3">
-        <v>1545478883.7027836</v>
+        <v>1720297107.4505036</v>
       </c>
       <c r="D3">
-        <v>1513279025.9688597</v>
-      </c>
-      <c r="F3">
-        <v>1292532946.0532973</v>
+        <v>1653869522.4505036</v>
+      </c>
+      <c r="E3">
+        <v>1619411359.4209394</v>
       </c>
       <c r="H3">
-        <v>1019558119.1714649</v>
-      </c>
-      <c r="I3">
-        <v>926002874.1450098</v>
+        <v>1383183470.6916733</v>
+      </c>
+      <c r="J3">
+        <v>1091063823.2886567</v>
+      </c>
+      <c r="K3">
+        <v>990947173.33228</v>
       </c>
     </row>
     <row r="4">
@@ -3076,22 +3557,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-134762652.4199814</v>
+        <v>-150527720.9005968</v>
       </c>
       <c r="C7">
-        <v>-136272000.4199814</v>
+        <v>-144214098.9005968</v>
       </c>
       <c r="D7">
-        <v>-124492415.30039065</v>
-      </c>
-      <c r="F7">
-        <v>-114145495.30322978</v>
+        <v>-145829302.9005968</v>
+      </c>
+      <c r="E7">
+        <v>-133223568.18507205</v>
       </c>
       <c r="H7">
-        <v>-105772362.10919988</v>
-      </c>
-      <c r="I7">
-        <v>-140369092.74821365</v>
+        <v>-122150977.14873347</v>
+      </c>
+      <c r="J7">
+        <v>-113190602.50819075</v>
+      </c>
+      <c r="K7">
+        <v>-150213740.76240343</v>
       </c>
     </row>
     <row r="8">
@@ -3099,22 +3583,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>1472790311.282802</v>
+        <v>1631791472.5499067</v>
       </c>
       <c r="C8">
-        <v>1409206883.282802</v>
+        <v>1576083008.5499067</v>
       </c>
       <c r="D8">
-        <v>1388786610.668469</v>
-      </c>
-      <c r="F8">
-        <v>1178387450.7500675</v>
+        <v>1508040219.5499067</v>
+      </c>
+      <c r="E8">
+        <v>1486187791.2358677</v>
       </c>
       <c r="H8">
-        <v>913785757.062265</v>
-      </c>
-      <c r="I8">
-        <v>785633781.3967962</v>
+        <v>1261032493.54294</v>
+      </c>
+      <c r="J8">
+        <v>977873220.780466</v>
+      </c>
+      <c r="K8">
+        <v>840733432.5698768</v>
       </c>
     </row>
     <row r="9">
@@ -3142,22 +3629,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>1472790311.282802</v>
+        <v>1631791472.5499067</v>
       </c>
       <c r="C13">
-        <v>1409206883.282802</v>
+        <v>1576083008.5499067</v>
       </c>
       <c r="D13">
-        <v>1388786610.668469</v>
-      </c>
-      <c r="F13">
-        <v>1178387450.7500675</v>
+        <v>1508040219.5499067</v>
+      </c>
+      <c r="E13">
+        <v>1486187791.2358677</v>
       </c>
       <c r="H13">
-        <v>913785757.062265</v>
-      </c>
-      <c r="I13">
-        <v>785633781.3967962</v>
+        <v>1261032493.54294</v>
+      </c>
+      <c r="J13">
+        <v>977873220.780466</v>
+      </c>
+      <c r="K13">
+        <v>840733432.5698768</v>
       </c>
     </row>
     <row r="14"/>
@@ -3166,22 +3656,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-286229743.19644153</v>
+        <v>-333887752.6003381</v>
       </c>
       <c r="C15">
-        <v>-230860795.19644153</v>
+        <v>-306304184.6003381</v>
       </c>
       <c r="D15">
-        <v>-231674129.96669632</v>
-      </c>
-      <c r="F15">
-        <v>-215866146.24057806</v>
+        <v>-247051989.60033813</v>
+      </c>
+      <c r="E15">
+        <v>-247922366.80332577</v>
       </c>
       <c r="H15">
-        <v>-212991312.99062726</v>
-      </c>
-      <c r="I15">
-        <v>-244781095.5286438</v>
+        <v>-231005705.71418697</v>
+      </c>
+      <c r="J15">
+        <v>-227929248.86682487</v>
+      </c>
+      <c r="K15">
+        <v>-261948576.4806636</v>
       </c>
     </row>
     <row r="16">
@@ -3189,22 +3682,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-11012638.763050426</v>
+        <v>-11024334.380477937</v>
       </c>
       <c r="C16">
-        <v>-10681544.763050426</v>
+        <v>-11784998.380477937</v>
       </c>
       <c r="D16">
-        <v>-11573727.778434817</v>
-      </c>
-      <c r="F16">
-        <v>-11375884.661293674</v>
+        <v>-11430684.380477937</v>
+      </c>
+      <c r="E16">
+        <v>-12385439.772578139</v>
       </c>
       <c r="H16">
-        <v>-13865122.630763656</v>
-      </c>
-      <c r="I16">
-        <v>-18376634.710318897</v>
+        <v>-12173721.123351179</v>
+      </c>
+      <c r="J16">
+        <v>-14837539.345163073</v>
+      </c>
+      <c r="K16">
+        <v>-19665461.879223812</v>
       </c>
     </row>
     <row r="17">
@@ -3212,22 +3708,25 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
-        <v>-203721487.53554627</v>
+        <v>-262193111.99326387</v>
       </c>
       <c r="C17">
-        <v>-175537312.53554627</v>
+        <v>-218009292.99326387</v>
       </c>
       <c r="D17">
-        <v>-197608792.9271934</v>
-      </c>
-      <c r="F17">
-        <v>-155590032.61095032</v>
+        <v>-187848448.99326387</v>
+      </c>
+      <c r="E17">
+        <v>-211467890.9151434</v>
       </c>
       <c r="H17">
-        <v>-173263976.39978975</v>
-      </c>
-      <c r="I17">
-        <v>-168924846.2678411</v>
+        <v>-166502186.24521685</v>
+      </c>
+      <c r="J17">
+        <v>-185415674.66754478</v>
+      </c>
+      <c r="K17">
+        <v>-180772223.91913804</v>
       </c>
     </row>
     <row r="18">
@@ -3235,22 +3734,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>74314816.19392009</v>
+        <v>73841447.86161412</v>
       </c>
       <c r="C18">
-        <v>92090973.19392009</v>
+        <v>79526810.86161412</v>
       </c>
       <c r="D18">
-        <v>78375558.19608285</v>
-      </c>
-      <c r="F18">
-        <v>55731387.10334759</v>
+        <v>98549682.86161412</v>
+      </c>
+      <c r="E18">
+        <v>83872350.74670577</v>
       </c>
       <c r="H18">
-        <v>41260020.44981914</v>
-      </c>
-      <c r="I18">
-        <v>40906417.72085577</v>
+        <v>59640053.02568963</v>
+      </c>
+      <c r="J18">
+        <v>44153751.33055756</v>
+      </c>
+      <c r="K18">
+        <v>43775349.022603214</v>
       </c>
     </row>
     <row r="19">
@@ -3258,22 +3760,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-32191892.145161886</v>
+        <v>-34151758.15895295</v>
       </c>
       <c r="C19">
-        <v>-21709138.145161886</v>
+        <v>-34449638.15895295</v>
       </c>
       <c r="D19">
-        <v>-51513678.3846523</v>
-      </c>
-      <c r="F19">
-        <v>-65249955.2332158</v>
+        <v>-23231687.15895295</v>
+      </c>
+      <c r="E19">
+        <v>-55126539.46171822</v>
       </c>
       <c r="H19">
-        <v>-98931590.53778487</v>
-      </c>
-      <c r="I19">
-        <v>-39178034.71025356</v>
+        <v>-69826196.55269831</v>
+      </c>
+      <c r="J19">
+        <v>-105870060.1628287</v>
+      </c>
+      <c r="K19">
+        <v>-41925747.572528675</v>
       </c>
     </row>
     <row r="20">
@@ -3286,22 +3791,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>1013949365.8365221</v>
+        <v>1064375963.2784879</v>
       </c>
       <c r="C21">
-        <v>1062509065.8365221</v>
+        <v>1085061705.278488</v>
       </c>
       <c r="D21">
-        <v>974791839.807575</v>
-      </c>
-      <c r="F21">
-        <v>786036819.1073773</v>
+        <v>1137027092.278488</v>
+      </c>
+      <c r="E21">
+        <v>1043157905.0298078</v>
       </c>
       <c r="H21">
-        <v>455993774.95311856</v>
-      </c>
-      <c r="I21">
-        <v>355279587.9005946</v>
+        <v>841164736.9331763</v>
+      </c>
+      <c r="J21">
+        <v>487974449.068662</v>
+      </c>
+      <c r="K21">
+        <v>380196771.74092585</v>
       </c>
     </row>
     <row r="22"/>
@@ -3320,22 +3828,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>115571051.89245191</v>
+        <v>202553770.27413365</v>
       </c>
       <c r="C25">
-        <v>44868504.89245191</v>
+        <v>123676513.27413365</v>
       </c>
       <c r="D25">
-        <v>13000416.509249195</v>
-      </c>
-      <c r="F25">
-        <v>52816.95674000461</v>
+        <v>48015313.27413365</v>
+      </c>
+      <c r="E25">
+        <v>13912187.911811378</v>
       </c>
       <c r="H25">
-        <v>37247.812331834575</v>
-      </c>
-      <c r="I25">
-        <v>11870266.6394058</v>
+        <v>56521.22196040264</v>
+      </c>
+      <c r="J25">
+        <v>39860.150949447925</v>
+      </c>
+      <c r="K25">
+        <v>12702776.094383499</v>
       </c>
     </row>
     <row r="26">
@@ -3343,19 +3854,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-0.5162370833295427</v>
+        <v>-0.9365571293201356</v>
       </c>
       <c r="C26">
-        <v>-6821.5162370833295</v>
-      </c>
-      <c r="F26">
+        <v>-0.9365571293201356</v>
+      </c>
+      <c r="D26">
+        <v>-7299.93655712932</v>
+      </c>
+      <c r="H26">
         <v>0</v>
       </c>
-      <c r="H26">
-        <v>-45738000.77083173</v>
-      </c>
-      <c r="I26">
-        <v>-10342.021145039527</v>
+      <c r="J26">
+        <v>-48945790.389229104</v>
+      </c>
+      <c r="K26">
+        <v>-11067.348608050559</v>
       </c>
     </row>
     <row r="27">
@@ -3393,22 +3907,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>1129520417.2127368</v>
+        <v>1266929732.6160643</v>
       </c>
       <c r="C33">
-        <v>1107370749.2127368</v>
+        <v>1208738217.6160643</v>
       </c>
       <c r="D33">
-        <v>987785435.1303263</v>
-      </c>
-      <c r="F33">
-        <v>786089636.0641173</v>
+        <v>1185035105.6160643</v>
+      </c>
+      <c r="E33">
+        <v>1057062793.3579271</v>
       </c>
       <c r="H33">
-        <v>410293021.9946187</v>
-      </c>
-      <c r="I33">
-        <v>367139512.5188553</v>
+        <v>841221258.1551367</v>
+      </c>
+      <c r="J33">
+        <v>439068518.8303824</v>
+      </c>
+      <c r="K33">
+        <v>392888480.4867012</v>
       </c>
     </row>
     <row r="34"/>
@@ -3417,22 +3934,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>40635369.775151044</v>
+        <v>17783955.289117135</v>
       </c>
       <c r="C35">
-        <v>54710264.775151044</v>
+        <v>43485291.289117135</v>
       </c>
       <c r="D35">
-        <v>61303656.19821367</v>
-      </c>
-      <c r="F35">
-        <v>20151619.49438084</v>
+        <v>58547315.289117135</v>
+      </c>
+      <c r="E35">
+        <v>65603127.72316585</v>
       </c>
       <c r="H35">
-        <v>8661908.938216096</v>
-      </c>
-      <c r="I35">
-        <v>3207269.0673849643</v>
+        <v>21564933.472222935</v>
+      </c>
+      <c r="J35">
+        <v>9269403.38701659</v>
+      </c>
+      <c r="K35">
+        <v>3432207.723302903</v>
       </c>
     </row>
     <row r="36">
@@ -3440,22 +3960,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-18081819.718782995</v>
+        <v>-20555872.625566687</v>
       </c>
       <c r="C36">
-        <v>-16854915.718782995</v>
+        <v>-19349970.625566687</v>
       </c>
       <c r="D36">
-        <v>-16499379.470150022</v>
-      </c>
-      <c r="F36">
-        <v>-17701662.96939272</v>
+        <v>-18037018.625566687</v>
+      </c>
+      <c r="E36">
+        <v>-17656547.192445807</v>
       </c>
       <c r="H36">
-        <v>-76131812.56349748</v>
-      </c>
-      <c r="I36">
-        <v>-127430875.19800904</v>
+        <v>-18943151.660297625</v>
+      </c>
+      <c r="J36">
+        <v>-81471242.22494225</v>
+      </c>
+      <c r="K36">
+        <v>-136368114.07234457</v>
       </c>
     </row>
     <row r="37">
@@ -3463,22 +3986,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-225835570.47881964</v>
+        <v>-270259577.96506417</v>
       </c>
       <c r="C37">
-        <v>-189879041.47881964</v>
+        <v>-241674325.96506417</v>
       </c>
       <c r="D37">
-        <v>-183690903.7335564</v>
-      </c>
-      <c r="F37">
-        <v>-119706632.1505235</v>
+        <v>-203196020.96506417</v>
+      </c>
+      <c r="E37">
+        <v>-196573884.27621073</v>
       </c>
       <c r="H37">
-        <v>-36677611.66790409</v>
-      </c>
-      <c r="I37">
-        <v>63869979.962057725</v>
+        <v>-128102138.84942245</v>
+      </c>
+      <c r="J37">
+        <v>-39249959.823771544</v>
+      </c>
+      <c r="K37">
+        <v>68349438.07558759</v>
       </c>
     </row>
     <row r="38">
@@ -3486,22 +4012,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>926238396.7902853</v>
+        <v>993898237.3145508</v>
       </c>
       <c r="C38">
-        <v>955347056.7902853</v>
+        <v>991199212.3145508</v>
       </c>
       <c r="D38">
-        <v>848898808.1248336</v>
-      </c>
-      <c r="F38">
-        <v>668832960.438582</v>
+        <v>1022349381.3145508</v>
+      </c>
+      <c r="E38">
+        <v>908435489.6124365</v>
       </c>
       <c r="H38">
-        <v>306145506.7014332</v>
-      </c>
-      <c r="I38">
-        <v>306785886.350289</v>
+        <v>715740901.1176397</v>
+      </c>
+      <c r="J38">
+        <v>327616720.16868514</v>
+      </c>
+      <c r="K38">
+        <v>328302012.2132472</v>
       </c>
     </row>
     <row r="39"/>
@@ -3509,8 +4038,8 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
-      <c r="I40">
-        <v>9097452.03124833</v>
+      <c r="K40">
+        <v>9735492.86573791</v>
       </c>
     </row>
     <row r="41">
@@ -3528,22 +4057,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>926238396.7902853</v>
+        <v>993898237.3145508</v>
       </c>
       <c r="C43">
-        <v>955347056.7902853</v>
+        <v>991199212.3145508</v>
       </c>
       <c r="D43">
-        <v>848898808.1248336</v>
-      </c>
-      <c r="F43">
-        <v>668832960.438582</v>
+        <v>1022349381.3145508</v>
+      </c>
+      <c r="E43">
+        <v>908435489.6124365</v>
       </c>
       <c r="H43">
-        <v>306145506.7014332</v>
-      </c>
-      <c r="I43">
-        <v>315883338.38153726</v>
+        <v>715740901.1176397</v>
+      </c>
+      <c r="J43">
+        <v>327616720.16868514</v>
+      </c>
+      <c r="K43">
+        <v>338037505.07898504</v>
       </c>
     </row>
     <row r="44">
@@ -3557,22 +4089,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>926238396.7902853</v>
+        <v>993898237.3145508</v>
       </c>
       <c r="C46">
-        <v>955347056.7902853</v>
+        <v>991199212.3145508</v>
       </c>
       <c r="D46">
-        <v>848898808.1248336</v>
-      </c>
-      <c r="F46">
-        <v>668832960.438582</v>
+        <v>1022349381.3145508</v>
+      </c>
+      <c r="E46">
+        <v>908435489.6124365</v>
       </c>
       <c r="H46">
-        <v>306145506.7014332</v>
-      </c>
-      <c r="I46">
-        <v>315883338.38153726</v>
+        <v>715740901.1176397</v>
+      </c>
+      <c r="J46">
+        <v>327616720.16868514</v>
+      </c>
+      <c r="K46">
+        <v>338037505.07898504</v>
       </c>
     </row>
     <row r="47">
@@ -3585,7 +4120,10 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="F47">
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -3594,22 +4132,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>926238396.7902853</v>
+        <v>993898237.3145508</v>
       </c>
       <c r="C48">
-        <v>955347056.7902853</v>
+        <v>991199212.3145508</v>
       </c>
       <c r="D48">
-        <v>848898808.1248336</v>
-      </c>
-      <c r="F48">
-        <v>668832960.438582</v>
+        <v>1022349381.3145508</v>
+      </c>
+      <c r="E48">
+        <v>908435489.6124365</v>
       </c>
       <c r="H48">
-        <v>306145506.7014332</v>
-      </c>
-      <c r="I48">
-        <v>315883338.38153726</v>
+        <v>715740901.1176397</v>
+      </c>
+      <c r="J48">
+        <v>327616720.16868514</v>
+      </c>
+      <c r="K48">
+        <v>338037505.07898504</v>
       </c>
     </row>
     <row r="49"/>
@@ -3618,34 +4159,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>278835765.53229916</v>
+        <v>340402659.6356069</v>
       </c>
       <c r="C50">
-        <v>249292175.53229913</v>
+        <v>298391637.2109495</v>
       </c>
       <c r="D50">
-        <v>265595195.24302733</v>
-      </c>
-      <c r="F50">
-        <v>216135364.49310306</v>
+        <v>266776036.6356069</v>
+      </c>
+      <c r="E50">
+        <v>284222452.5703772</v>
       </c>
       <c r="H50">
-        <v>227972426.51804158</v>
-      </c>
-      <c r="I50">
-        <v>250206367.5504006</v>
+        <v>231293805.32359198</v>
+      </c>
+      <c r="J50">
+        <v>243961048.03058904</v>
+      </c>
+      <c r="K50">
+        <v>267754344.6101443</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3656,6 +4200,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3663,27 +4209,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3697,28 +4249,34 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>206854994</v>
+        <v>603208313</v>
       </c>
       <c r="C3">
-        <v>1098761973.7130969</v>
+        <v>221362565.18990678</v>
       </c>
       <c r="D3">
-        <v>651823365.1144743</v>
+        <v>1175822562.1289861</v>
       </c>
       <c r="E3">
-        <v>93439188</v>
+        <v>697538354.5850347</v>
       </c>
       <c r="F3">
-        <v>691390792.4809455</v>
+        <v>396129112</v>
       </c>
       <c r="G3">
-        <v>341080203.01612014</v>
+        <v>99992453.38472202</v>
       </c>
       <c r="H3">
-        <v>323958688.4400544</v>
+        <v>739880804.4840561</v>
       </c>
       <c r="I3">
-        <v>543298975.7907176</v>
+        <v>365001526.98823667</v>
+      </c>
+      <c r="J3">
+        <v>346679211.85721165</v>
+      </c>
+      <c r="K3">
+        <v>581402714.1451674</v>
       </c>
     </row>
     <row r="4">
@@ -3726,28 +4284,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>233879775</v>
+        <v>443669219</v>
       </c>
       <c r="C4">
-        <v>955347056.7902853</v>
+        <v>250282702.57781753</v>
       </c>
       <c r="D4">
-        <v>556895094.4819643</v>
+        <v>1022349381.3145508</v>
       </c>
       <c r="E4">
-        <v>262988435</v>
+        <v>595952383.2245651</v>
       </c>
       <c r="F4">
-        <v>668832960.438582</v>
+        <v>472120363</v>
       </c>
       <c r="G4">
-        <v>376829246.79571277</v>
+        <v>281432869.7661467</v>
       </c>
       <c r="H4">
-        <v>306145506.7014332</v>
+        <v>715740901.1176397</v>
       </c>
       <c r="I4">
-        <v>315883338.38153726</v>
+        <v>403257794.7297682</v>
+      </c>
+      <c r="J4">
+        <v>327616720.16868514</v>
+      </c>
+      <c r="K4">
+        <v>338037505.07898504</v>
       </c>
     </row>
     <row r="5">
@@ -3755,16 +4319,22 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>125511785</v>
+        <v>298650455</v>
       </c>
       <c r="C5">
-        <v>272299838.0969074</v>
-      </c>
-      <c r="E5">
-        <v>57417891</v>
+        <v>134314430.37417826</v>
+      </c>
+      <c r="D5">
+        <v>291397318.9447276</v>
       </c>
       <c r="F5">
-        <v>262394013.8437791</v>
+        <v>132644548</v>
+      </c>
+      <c r="G5">
+        <v>61444838.211421</v>
+      </c>
+      <c r="H5">
+        <v>280796759.4678176</v>
       </c>
     </row>
     <row r="6">
@@ -3772,28 +4342,34 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>82636625</v>
+        <v>215214529</v>
       </c>
       <c r="C6">
-        <v>249292175.53229913</v>
+        <v>88432263.27248536</v>
       </c>
       <c r="D6">
-        <v>222763720.27751082</v>
+        <v>266776036.6356069</v>
       </c>
       <c r="E6">
-        <v>53093035</v>
+        <v>238387034.3100184</v>
       </c>
       <c r="F6">
-        <v>216135364.49310306</v>
+        <v>141587906</v>
       </c>
       <c r="G6">
-        <v>173303889.52758655</v>
+        <v>56816662.69714282</v>
       </c>
       <c r="H6">
-        <v>227972426.51804158</v>
+        <v>231293805.32359198</v>
       </c>
       <c r="I6">
-        <v>250206367.5504006</v>
+        <v>185458387.0632332</v>
+      </c>
+      <c r="J6">
+        <v>243961048.03058904</v>
+      </c>
+      <c r="K6">
+        <v>267754344.6101443</v>
       </c>
     </row>
     <row r="7">
@@ -3801,28 +4377,34 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>-1159264</v>
+        <v>3833652</v>
       </c>
       <c r="C7">
-        <v>-3885775.1004789593</v>
+        <v>-1240567.8384168579</v>
       </c>
       <c r="D7">
-        <v>254097.2354880287</v>
+        <v>-4158300.1084957616</v>
       </c>
       <c r="E7">
-        <v>-1024383</v>
+        <v>271918.09473690466</v>
       </c>
       <c r="F7">
-        <v>12604467.35618563</v>
+        <v>1908435</v>
       </c>
       <c r="G7">
-        <v>3135025.3529439713</v>
+        <v>-1096227.0923801446</v>
       </c>
       <c r="H7">
-        <v>1922666.249267942</v>
+        <v>13488469.255026512</v>
       </c>
       <c r="I7">
-        <v>3999688.8292300473</v>
+        <v>3354897.267131343</v>
+      </c>
+      <c r="J7">
+        <v>2057510.552256758</v>
+      </c>
+      <c r="K7">
+        <v>4280203.064373579</v>
       </c>
     </row>
     <row r="8">
@@ -3830,28 +4412,34 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>5613784</v>
+        <v>11525076</v>
       </c>
       <c r="C8">
-        <v>69365078.09480146</v>
+        <v>6007501.20957706</v>
       </c>
       <c r="D8">
-        <v>10435350.823533954</v>
+        <v>74229929.50154959</v>
       </c>
       <c r="E8">
-        <v>10681598</v>
+        <v>11167223.871588433</v>
       </c>
       <c r="F8">
-        <v>82730220.99075378</v>
+        <v>14753011</v>
       </c>
       <c r="G8">
-        <v>16654666.371059805</v>
+        <v>11430741.351148514</v>
       </c>
       <c r="H8">
-        <v>56226437.42086944</v>
+        <v>88532423.5258305</v>
       </c>
       <c r="I8">
-        <v>55893049.05990699</v>
+        <v>17822724.987146668</v>
+      </c>
+      <c r="J8">
+        <v>60169823.20945766</v>
+      </c>
+      <c r="K8">
+        <v>59813052.984286755</v>
       </c>
     </row>
     <row r="9">
@@ -3874,28 +4462,34 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-17912</v>
+        <v>1126191</v>
       </c>
       <c r="C12">
-        <v>-42734731.53231053</v>
+        <v>-19168.240471301408</v>
       </c>
       <c r="D12">
-        <v>-44943058.08866067</v>
+        <v>-45731889.82178624</v>
       </c>
       <c r="E12">
-        <v>-14607566</v>
+        <v>-48095095.18530123</v>
       </c>
       <c r="F12">
-        <v>-7624876.047429188</v>
+        <v>-40390762</v>
       </c>
       <c r="G12">
-        <v>-3166588.843194089</v>
+        <v>-15632053.24857115</v>
       </c>
       <c r="H12">
-        <v>60075808.65895308</v>
+        <v>-8159639.21622314</v>
       </c>
       <c r="I12">
-        <v>70308454.26035722</v>
+        <v>-3388674.431670637</v>
+      </c>
+      <c r="J12">
+        <v>64289166.30653774</v>
+      </c>
+      <c r="K12">
+        <v>75239468.4249678</v>
       </c>
     </row>
     <row r="13">
@@ -3913,28 +4507,34 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
-        <v>-8164</v>
+        <v>-35742</v>
       </c>
       <c r="C15">
-        <v>-328716.9719027739</v>
+        <v>-8736.574096008526</v>
       </c>
       <c r="D15">
-        <v>-334666.47216992057</v>
+        <v>-351771.21284225094</v>
       </c>
       <c r="E15">
-        <v>3119</v>
+        <v>-358137.97544858966</v>
       </c>
       <c r="F15">
-        <v>140541.50148981038</v>
+        <v>-237646</v>
       </c>
       <c r="G15">
-        <v>63968.71950748689</v>
+        <v>3337.747991848431</v>
       </c>
       <c r="H15">
-        <v>-751558.0986867505</v>
+        <v>150398.24122121764</v>
       </c>
       <c r="I15">
-        <v>47592563.09982122</v>
+        <v>68455.10262174733</v>
+      </c>
+      <c r="J15">
+        <v>-804267.8854277417</v>
+      </c>
+      <c r="K15">
+        <v>50930420.6198615</v>
       </c>
     </row>
     <row r="16">
@@ -3961,8 +4561,8 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="I20">
-        <v>-12815663.566122796</v>
+      <c r="K20">
+        <v>-13714477.503055936</v>
       </c>
     </row>
     <row r="21">
@@ -3975,28 +4575,34 @@
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B22">
+        <v>-97748</v>
+      </c>
+      <c r="C22">
         <v>0</v>
       </c>
-      <c r="C22">
-        <v>-211314.0446857738</v>
-      </c>
       <c r="D22">
-        <v>-170048.5046833887</v>
+        <v>-226134.34700202345</v>
       </c>
       <c r="E22">
-        <v>-168172</v>
+        <v>-181974.6890105191</v>
       </c>
       <c r="F22">
-        <v>-52816.95674000461</v>
+        <v>-181976</v>
       </c>
       <c r="G22">
-        <v>-52817.11309626338</v>
+        <v>-179966.57752008154</v>
       </c>
       <c r="H22">
-        <v>-37247.812331834575</v>
+        <v>-56521.22196040264</v>
       </c>
       <c r="I22">
-        <v>-32110.103848278402</v>
+        <v>-56521.389282553566</v>
+      </c>
+      <c r="J22">
+        <v>-39860.150949447925</v>
+      </c>
+      <c r="K22">
+        <v>-34362.11434358314</v>
       </c>
     </row>
     <row r="23">
@@ -4029,16 +4635,22 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-98981789</v>
+        <v>-80545893</v>
       </c>
       <c r="C28">
-        <v>-66637289.21354518</v>
-      </c>
-      <c r="E28">
-        <v>-166301058</v>
+        <v>-105923779.24473071</v>
+      </c>
+      <c r="D28">
+        <v>-71310829.83479755</v>
       </c>
       <c r="F28">
-        <v>-189900687.8808038</v>
+        <v>-143456592</v>
+      </c>
+      <c r="G28">
+        <v>-177964418.8463512</v>
+      </c>
+      <c r="H28">
+        <v>-203219185.5161233</v>
       </c>
     </row>
     <row r="29">
@@ -4056,28 +4668,34 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-45767992</v>
+        <v>28348613</v>
       </c>
       <c r="C31">
-        <v>-63966881.83965827</v>
+        <v>-48977885.02370473</v>
       </c>
       <c r="D31">
-        <v>9015024.767671848</v>
+        <v>-68453136.0708962</v>
       </c>
       <c r="E31">
-        <v>-102392229</v>
+        <v>9647284.647246096</v>
       </c>
       <c r="F31">
-        <v>-134160787.91254087</v>
+        <v>-66621188</v>
       </c>
       <c r="G31">
-        <v>-67891113.03988452</v>
+        <v>-109573407.09382324</v>
       </c>
       <c r="H31">
-        <v>-84985304.97447746</v>
+        <v>-143570022.58412522</v>
       </c>
       <c r="I31">
-        <v>50272691.104305625</v>
+        <v>-72652589.35980423</v>
+      </c>
+      <c r="J31">
+        <v>-90945665.60281776</v>
+      </c>
+      <c r="K31">
+        <v>53798516.76120955</v>
       </c>
     </row>
     <row r="32">
@@ -4090,28 +4708,34 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1074110</v>
+        <v>210616</v>
       </c>
       <c r="C33">
-        <v>-5875057.5444225315</v>
+        <v>-1149441.6465291176</v>
       </c>
       <c r="D33">
-        <v>-7831702.788876283</v>
+        <v>-6287098.91660477</v>
       </c>
       <c r="E33">
-        <v>-3518656</v>
+        <v>-8380971.547395181</v>
       </c>
       <c r="F33">
-        <v>-824849.9524000604</v>
+        <v>-7430559</v>
       </c>
       <c r="G33">
-        <v>-284738.602378223</v>
+        <v>-3765433.471627263</v>
       </c>
       <c r="H33">
-        <v>190393.78434435528</v>
+        <v>-882699.9910867506</v>
       </c>
       <c r="I33">
-        <v>346108.6105986541</v>
+        <v>-304708.4637029954</v>
+      </c>
+      <c r="J33">
+        <v>203746.86481429788</v>
+      </c>
+      <c r="K33">
+        <v>370382.5969820802</v>
       </c>
     </row>
     <row r="34">
@@ -4119,16 +4743,22 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B34">
-        <v>-79088702</v>
+        <v>-138815102</v>
       </c>
       <c r="C34">
-        <v>-32314003.299496</v>
-      </c>
-      <c r="E34">
-        <v>-56235603</v>
+        <v>-84635510.18864988</v>
+      </c>
+      <c r="D34">
+        <v>-34580314.081909694</v>
       </c>
       <c r="F34">
-        <v>-26602171.356532827</v>
+        <v>-63554218</v>
+      </c>
+      <c r="G34">
+        <v>-60179631.607449695</v>
+      </c>
+      <c r="H34">
+        <v>-28467888.43349641</v>
       </c>
     </row>
     <row r="35">
@@ -4146,28 +4776,34 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>55553</v>
+        <v>71787</v>
       </c>
       <c r="C37">
-        <v>-117955.33908198084</v>
+        <v>59449.15491861362</v>
       </c>
       <c r="D37">
-        <v>-129352.20362197896</v>
+        <v>-126228.0205670671</v>
       </c>
       <c r="E37">
-        <v>-154128</v>
+        <v>-138424.19297224417</v>
       </c>
       <c r="F37">
-        <v>364047.12197662407</v>
+        <v>-150895</v>
       </c>
       <c r="G37">
-        <v>319822.9272753191</v>
+        <v>-164937.61541763865</v>
       </c>
       <c r="H37">
-        <v>162379.83743859918</v>
+        <v>389579.2081807239</v>
       </c>
       <c r="I37">
-        <v>193984.66821294717</v>
+        <v>342253.3931581543</v>
+      </c>
+      <c r="J37">
+        <v>173768.18734445627</v>
+      </c>
+      <c r="K37">
+        <v>207589.59178491458</v>
       </c>
     </row>
     <row r="38">
@@ -4180,28 +4816,34 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-8983772</v>
+        <v>-5664383</v>
       </c>
       <c r="C39">
-        <v>-2788720.350132475</v>
+        <v>-9613839.997506944</v>
       </c>
       <c r="D39">
-        <v>-2079174.5839178907</v>
+        <v>-2984304.5041620783</v>
       </c>
       <c r="E39">
-        <v>-8339759</v>
+        <v>-2224995.444749675</v>
       </c>
       <c r="F39">
-        <v>-2868996.1380813746</v>
+        <v>-4903230</v>
       </c>
       <c r="G39">
-        <v>-2008105.629373786</v>
+        <v>-8924659.780298134</v>
       </c>
       <c r="H39">
-        <v>-610946.3439513901</v>
+        <v>-3070210.3554030177</v>
       </c>
       <c r="I39">
-        <v>1821253.3499385251</v>
+        <v>-2148942.1391028804</v>
+      </c>
+      <c r="J39">
+        <v>-653794.463818818</v>
+      </c>
+      <c r="K39">
+        <v>1948985.1591550305</v>
       </c>
     </row>
     <row r="40">
@@ -4209,28 +4851,34 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>8228277</v>
+        <v>3953485</v>
       </c>
       <c r="C40">
-        <v>-9694830.431256706</v>
+        <v>8805359.10007138</v>
       </c>
       <c r="D40">
-        <v>-5151733.256401423</v>
+        <v>-10374767.81123377</v>
       </c>
       <c r="E40">
-        <v>-468011</v>
+        <v>-5513044.992334925</v>
       </c>
       <c r="F40">
-        <v>5319536.987173686</v>
+        <v>-7337869</v>
       </c>
       <c r="G40">
-        <v>-2277779.0557136154</v>
+        <v>-500834.4903536313</v>
       </c>
       <c r="H40">
-        <v>-1192901.496938127</v>
+        <v>5692617.472427837</v>
       </c>
       <c r="I40">
-        <v>-3871529.759071281</v>
+        <v>-2437528.8454897515</v>
+      </c>
+      <c r="J40">
+        <v>-1276564.4680597053</v>
+      </c>
+      <c r="K40">
+        <v>-4143055.684104395</v>
       </c>
     </row>
     <row r="41">
@@ -4243,28 +4891,34 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>3725111</v>
+        <v>-3356926</v>
       </c>
       <c r="C42">
-        <v>843171.9793959367</v>
+        <v>3986367.989632094</v>
       </c>
       <c r="D42">
-        <v>-60998995.38902715</v>
+        <v>902307.0153932845</v>
       </c>
       <c r="E42">
-        <v>-3165809</v>
+        <v>-65277099.82830942</v>
       </c>
       <c r="F42">
-        <v>2431702.7241588333</v>
+        <v>-3257782</v>
       </c>
       <c r="G42">
-        <v>-49480196.699847355</v>
+        <v>-3387839.8949425104</v>
       </c>
       <c r="H42">
-        <v>-61545712.338498816</v>
+        <v>2602247.7987603415</v>
       </c>
       <c r="I42">
-        <v>-43997841.45256325</v>
+        <v>-52950441.54253955</v>
+      </c>
+      <c r="J42">
+        <v>-65862160.232351914</v>
+      </c>
+      <c r="K42">
+        <v>-47083586.71175333</v>
       </c>
     </row>
     <row r="43">
@@ -4272,39 +4926,45 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B43">
-        <v>21016045</v>
+        <v>42000326</v>
       </c>
       <c r="C43">
-        <v>35372300.63973909</v>
+        <v>22489984.608960006</v>
       </c>
       <c r="D43">
-        <v>-32607681.842962444</v>
+        <v>37853102.09276951</v>
       </c>
       <c r="E43">
-        <v>18177684</v>
+        <v>-34894589.48066061</v>
       </c>
       <c r="F43">
-        <v>-13835860.52897233</v>
+        <v>21690549</v>
       </c>
       <c r="G43">
-        <v>-70409962.47256193</v>
+        <v>19452557.95686289</v>
       </c>
       <c r="H43">
-        <v>14572627.807491045</v>
+        <v>-14806224.974694569</v>
       </c>
       <c r="I43">
-        <v>76393.84373459412</v>
+        <v>-75348095.81561941</v>
+      </c>
+      <c r="J43">
+        <v>15594664.70035519</v>
+      </c>
+      <c r="K43">
+        <v>81751.65069404437</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="H44">
-        <v>-131925013.92225634</v>
-      </c>
-      <c r="I44">
-        <v>-34434772.24525276</v>
+      <c r="J44">
+        <v>-141177444.7879408</v>
+      </c>
+      <c r="K44">
+        <v>-36849821.06808287</v>
       </c>
     </row>
     <row r="45">
@@ -4322,28 +4982,34 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>4933553</v>
+        <v>9598477</v>
       </c>
       <c r="C47">
-        <v>5952476.636750933</v>
+        <v>5279562.878623854</v>
       </c>
       <c r="D47">
-        <v>1164227.2499925755</v>
+        <v>6369947.72069257</v>
       </c>
       <c r="E47">
-        <v>-2315604</v>
+        <v>1245879.181057371</v>
       </c>
       <c r="F47">
-        <v>-5135099.6504366975</v>
+        <v>-2354192</v>
       </c>
       <c r="G47">
-        <v>-3241270.5002167956</v>
+        <v>-2478006.6049747337</v>
       </c>
       <c r="H47">
-        <v>-19306178.694341324</v>
+        <v>-5495244.804804959</v>
       </c>
       <c r="I47">
-        <v>23618120.541520897</v>
+        <v>-3468593.8131247736</v>
+      </c>
+      <c r="J47">
+        <v>-20660198.514685705</v>
+      </c>
+      <c r="K47">
+        <v>25274554.154759716</v>
       </c>
     </row>
     <row r="48">
@@ -4351,28 +5017,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-2025752</v>
+        <v>-16892786</v>
       </c>
       <c r="C48">
-        <v>5952210.334616818</v>
+        <v>-2167826.12054599</v>
       </c>
       <c r="D48">
-        <v>9649992.252897048</v>
+        <v>6369662.741720668</v>
       </c>
       <c r="E48">
-        <v>-7888943</v>
+        <v>10326784.951413928</v>
       </c>
       <c r="F48">
-        <v>-14588209.175148768</v>
+        <v>-9537208</v>
       </c>
       <c r="G48">
-        <v>-25530156.53432208</v>
+        <v>-8442226.244327264</v>
       </c>
       <c r="H48">
-        <v>-79833946.0794899</v>
+        <v>-15611338.851881262</v>
       </c>
       <c r="I48">
-        <v>-178833662.35616323</v>
+        <v>-27320688.90798641</v>
+      </c>
+      <c r="J48">
+        <v>-85433021.22736561</v>
+      </c>
+      <c r="K48">
+        <v>-191375985.0606554</v>
       </c>
     </row>
     <row r="49">
@@ -4380,16 +5052,22 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>260409771</v>
+        <v>661773781</v>
       </c>
       <c r="C49">
-        <v>1161009605.6736476</v>
-      </c>
-      <c r="E49">
-        <v>154105268</v>
+        <v>278673353.7072651</v>
+      </c>
+      <c r="D49">
+        <v>1242435870.424481</v>
       </c>
       <c r="F49">
-        <v>741326286.4015572</v>
+        <v>461308319</v>
+      </c>
+      <c r="G49">
+        <v>164913289.1312165</v>
+      </c>
+      <c r="H49">
+        <v>793318475.0693339</v>
       </c>
     </row>
     <row r="50">
@@ -4457,28 +5135,34 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-53554777</v>
+        <v>-58565468</v>
       </c>
       <c r="C62">
-        <v>-62247631.96055062</v>
+        <v>-57310788.517358296</v>
       </c>
       <c r="D62">
-        <v>-2684219.5680353525</v>
+        <v>-66613308.29549472</v>
       </c>
       <c r="E62">
-        <v>-60666080</v>
+        <v>-2872474.662677224</v>
       </c>
       <c r="F62">
-        <v>-49935493.92061175</v>
+        <v>-65179207</v>
       </c>
       <c r="G62">
-        <v>-1433364.3978653012</v>
+        <v>-64920835.74649447</v>
       </c>
       <c r="H62">
-        <v>-892130.8095936707</v>
+        <v>-53437670.58527778</v>
       </c>
       <c r="I62">
-        <v>1488429.976140555</v>
+        <v>-1533891.9976152435</v>
+      </c>
+      <c r="J62">
+        <v>-954699.5249077874</v>
+      </c>
+      <c r="K62">
+        <v>1592819.5459667025</v>
       </c>
     </row>
     <row r="63">
@@ -4502,28 +5186,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-128926267</v>
+        <v>-263542536</v>
       </c>
       <c r="C67">
-        <v>-462933146.25752234</v>
+        <v>-137968383.7049582</v>
       </c>
       <c r="D67">
-        <v>-545305467.9912984</v>
+        <v>-495400506.34213567</v>
       </c>
       <c r="E67">
-        <v>-100374754</v>
+        <v>-583549929.6992385</v>
       </c>
       <c r="F67">
-        <v>-428780641.4426715</v>
+        <v>-200888918</v>
       </c>
       <c r="G67">
-        <v>-262316021.0887557</v>
+        <v>-107414438.47251691</v>
       </c>
       <c r="H67">
-        <v>-149915295.021638</v>
+        <v>-458852749.25256777</v>
       </c>
       <c r="I67">
-        <v>-321853774.78641135</v>
+        <v>-280713296.7677669</v>
+      </c>
+      <c r="J67">
+        <v>-160429456.52639863</v>
+      </c>
+      <c r="K67">
+        <v>-344426672.1584423</v>
       </c>
     </row>
     <row r="68">
@@ -4555,8 +5245,8 @@
       <c r="A73" t="str">
         <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
-      <c r="D73">
-        <v>-247124747.2646753</v>
+      <c r="E73">
+        <v>-264456597.92200094</v>
       </c>
     </row>
     <row r="74">
@@ -4573,11 +5263,11 @@
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
-      <c r="C76">
+      <c r="D76">
         <v>0</v>
       </c>
-      <c r="F76">
-        <v>-14431385.829128567</v>
+      <c r="H76">
+        <v>-15443516.85500602</v>
       </c>
     </row>
     <row r="77">
@@ -4585,28 +5275,34 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
+        <v>174506</v>
+      </c>
+      <c r="C77">
         <v>0</v>
       </c>
-      <c r="C77">
-        <v>2363340.1052344</v>
-      </c>
       <c r="D77">
-        <v>-351817993.07649034</v>
+        <v>2529090.6349153505</v>
       </c>
       <c r="E77">
-        <v>296746</v>
+        <v>-376492401.37454337</v>
       </c>
       <c r="F77">
-        <v>946326.6420157831</v>
+        <v>319567</v>
       </c>
       <c r="G77">
-        <v>-275572186.3141226</v>
+        <v>317557.9883260835</v>
       </c>
       <c r="H77">
-        <v>-249949429.30221963</v>
+        <v>1012696.328637656</v>
       </c>
       <c r="I77">
-        <v>-326426699.36305916</v>
+        <v>-294899170.07991165</v>
+      </c>
+      <c r="J77">
+        <v>-267479386.25108847</v>
+      </c>
+      <c r="K77">
+        <v>-349320314.2945695</v>
       </c>
     </row>
     <row r="78">
@@ -4614,28 +5310,34 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-131830300</v>
+        <v>-269128803</v>
       </c>
       <c r="C78">
-        <v>-520553466.11797816</v>
+        <v>-141076088.19806868</v>
       </c>
       <c r="D78">
-        <v>298623.276780252</v>
+        <v>-557061970.5626874</v>
       </c>
       <c r="E78">
-        <v>-117700130</v>
+        <v>319566.92606363713</v>
       </c>
       <c r="F78">
-        <v>-436399334.21864784</v>
+        <v>-247067842</v>
       </c>
       <c r="G78">
-        <v>334783.6036552408</v>
+        <v>-125954912.64757912</v>
       </c>
       <c r="H78">
-        <v>91817729.20504154</v>
+        <v>-467005771.5396871</v>
       </c>
       <c r="I78">
-        <v>952847.4078616782</v>
+        <v>358263.3218352231</v>
+      </c>
+      <c r="J78">
+        <v>98257275.17480296</v>
+      </c>
+      <c r="K78">
+        <v>1019674.4219712405</v>
       </c>
     </row>
     <row r="79">
@@ -4718,16 +5420,22 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B94">
-        <v>2904033</v>
+        <v>5411761</v>
       </c>
       <c r="C94">
-        <v>55256979.75522145</v>
-      </c>
-      <c r="E94">
-        <v>17028630</v>
+        <v>3107704.493110476</v>
+      </c>
+      <c r="D94">
+        <v>59132373.585636355</v>
       </c>
       <c r="F94">
-        <v>21103751.96308913</v>
+        <v>45859357</v>
+      </c>
+      <c r="G94">
+        <v>18222916.186736114</v>
+      </c>
+      <c r="H94">
+        <v>22583842.813487697</v>
       </c>
     </row>
     <row r="95">
@@ -4749,17 +5457,17 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="D98">
-        <v>53338649.07308699</v>
-      </c>
-      <c r="G98">
-        <v>12921381.621711679</v>
-      </c>
-      <c r="H98">
-        <v>8216405.07554006</v>
+      <c r="E98">
+        <v>57079502.671242155</v>
       </c>
       <c r="I98">
-        <v>3620077.16878612</v>
+        <v>13827609.990309516</v>
+      </c>
+      <c r="J98">
+        <v>8792654.549886853</v>
+      </c>
+      <c r="K98">
+        <v>3873967.7141558914</v>
       </c>
     </row>
     <row r="99">
@@ -4773,28 +5481,34 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>516332219</v>
+        <v>-110098786</v>
       </c>
       <c r="C101">
-        <v>-260319272.62406975</v>
+        <v>552544670.4372858</v>
       </c>
       <c r="D101">
-        <v>-248198105.74571306</v>
+        <v>-278576508.31690705</v>
       </c>
       <c r="E101">
-        <v>-11813039</v>
+        <v>-265605235.3425259</v>
       </c>
       <c r="F101">
-        <v>-125779135.12063907</v>
+        <v>-21708641</v>
       </c>
       <c r="G101">
-        <v>-111334486.19468285</v>
+        <v>-12641534.850874381</v>
       </c>
       <c r="H101">
-        <v>-153163269.57686755</v>
+        <v>-134600530.8321082</v>
       </c>
       <c r="I101">
-        <v>-99516160.4789292</v>
+        <v>-119142820.68604666</v>
+      </c>
+      <c r="J101">
+        <v>-163905224.57682896</v>
+      </c>
+      <c r="K101">
+        <v>-106495628.34081826</v>
       </c>
     </row>
     <row r="102">
@@ -4812,9 +5526,15 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>525203079</v>
-      </c>
-      <c r="E104">
+        <v>526061037</v>
+      </c>
+      <c r="C104">
+        <v>562037679.462925</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
         <v>0</v>
       </c>
     </row>
@@ -4848,20 +5568,26 @@
       <c r="C109">
         <v>0</v>
       </c>
-      <c r="E109">
+      <c r="D109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>66905434.55457942</v>
+        <v>0</v>
       </c>
       <c r="G109">
-        <v>60725643.80437869</v>
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>234410896.22294948</v>
+        <v>71597781.28512155</v>
       </c>
       <c r="I109">
-        <v>796683105.6093335</v>
+        <v>64984576.99960503</v>
+      </c>
+      <c r="J109">
+        <v>250851073.46442467</v>
+      </c>
+      <c r="K109">
+        <v>852557690.2491581</v>
       </c>
     </row>
     <row r="110">
@@ -4872,25 +5598,31 @@
         <v>0</v>
       </c>
       <c r="C110">
-        <v>-2751055.104485937</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>-31496923.96767066</v>
+        <v>-2943997.643623697</v>
       </c>
       <c r="E110">
-        <v>-3271697</v>
+        <v>-33705929.69621528</v>
       </c>
       <c r="F110">
-        <v>-132951023.53498565</v>
+        <v>-3302766</v>
       </c>
       <c r="G110">
-        <v>-145209578.93942183</v>
+        <v>-3501154.2454910344</v>
       </c>
       <c r="H110">
-        <v>-332100390.03996176</v>
+        <v>-142275412.57393134</v>
       </c>
       <c r="I110">
-        <v>-685521050.7412168</v>
+        <v>-155393709.6832996</v>
+      </c>
+      <c r="J110">
+        <v>-355391923.67680764</v>
+      </c>
+      <c r="K110">
+        <v>-733599394.1908697</v>
       </c>
     </row>
     <row r="111">
@@ -4908,16 +5640,22 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
-        <v>-10144374</v>
+        <v>-21636450</v>
       </c>
       <c r="C113">
-        <v>-38240497.871418126</v>
-      </c>
-      <c r="E113">
-        <v>-8409981</v>
+        <v>-10855839.67523547</v>
+      </c>
+      <c r="D113">
+        <v>-40922457.51125683</v>
       </c>
       <c r="F113">
-        <v>-29579965.121464368</v>
+        <v>-19612337</v>
+      </c>
+      <c r="G113">
+        <v>-8999806.731078377</v>
+      </c>
+      <c r="H113">
+        <v>-31654526.830110393</v>
       </c>
     </row>
     <row r="114">
@@ -4939,20 +5677,26 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="C117">
-        <v>-218030094.27352747</v>
+      <c r="B117">
+        <v>-616302963</v>
       </c>
       <c r="D117">
-        <v>-218030099.34143892</v>
+        <v>-233321420.11028868</v>
+      </c>
+      <c r="E117">
+        <v>-233321425.5336331</v>
       </c>
       <c r="F117">
-        <v>-18940628.146249007</v>
-      </c>
-      <c r="G117">
-        <v>-188166553.26629683</v>
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>-20269010.439079992</v>
       </c>
       <c r="I117">
-        <v>-150083629.04291373</v>
+        <v>-201363429.0790712</v>
+      </c>
+      <c r="K117">
+        <v>-160609596.48839697</v>
       </c>
     </row>
     <row r="118">
@@ -4960,16 +5704,22 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-65190</v>
+        <v>-332600</v>
       </c>
       <c r="C118">
-        <v>-1299353.0372438366</v>
-      </c>
-      <c r="E118">
-        <v>-131361</v>
+        <v>-69762.03641827483</v>
+      </c>
+      <c r="D118">
+        <v>-1390481.8822580234</v>
       </c>
       <c r="F118">
-        <v>-8951937.711685406</v>
+        <v>-335663</v>
+      </c>
+      <c r="G118">
+        <v>-140573.8743049701</v>
+      </c>
+      <c r="H118">
+        <v>-9579773.04274774</v>
       </c>
     </row>
     <row r="119">
@@ -4997,28 +5747,34 @@
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
       <c r="B123">
-        <v>1338704</v>
+        <v>2112190</v>
       </c>
       <c r="C123">
-        <v>1727.6626056171685</v>
+        <v>1432592.686014576</v>
       </c>
       <c r="D123">
-        <v>2125947.942041209</v>
+        <v>1848.8305201956819</v>
       </c>
       <c r="E123">
+        <v>2275049.2062591696</v>
+      </c>
+      <c r="F123">
+        <v>1542125</v>
+      </c>
+      <c r="G123">
         <v>0</v>
       </c>
-      <c r="F123">
-        <v>-2261015.160834066</v>
-      </c>
-      <c r="G123">
-        <v>112812.54888602467</v>
-      </c>
       <c r="H123">
-        <v>1942399.4595007156</v>
+        <v>-2419589.2313602953</v>
       </c>
       <c r="I123">
-        <v>318612.5685936767</v>
+        <v>120724.54584791017</v>
+      </c>
+      <c r="J123">
+        <v>2078627.7317460696</v>
+      </c>
+      <c r="K123">
+        <v>340958.14716294163</v>
       </c>
     </row>
     <row r="124">
@@ -5031,16 +5787,22 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>594260946</v>
+        <v>229566991</v>
       </c>
       <c r="C125">
-        <v>375509554.8315049</v>
-      </c>
-      <c r="E125">
-        <v>-18748605</v>
+        <v>635938851.9222343</v>
+      </c>
+      <c r="D125">
+        <v>401845547.46994346</v>
       </c>
       <c r="F125">
-        <v>136831015.91763496</v>
+        <v>173531553</v>
+      </c>
+      <c r="G125">
+        <v>-20063519.938669268</v>
+      </c>
+      <c r="H125">
+        <v>146427524.39938018</v>
       </c>
     </row>
     <row r="126">
@@ -5053,28 +5815,34 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>594260946</v>
+        <v>229566991</v>
       </c>
       <c r="C127">
-        <v>375509554.8315049</v>
+        <v>635938851.9222343</v>
       </c>
       <c r="D127">
-        <v>-141680208.62253729</v>
+        <v>401845547.46994346</v>
       </c>
       <c r="E127">
-        <v>-18748605</v>
+        <v>-151616810.45672992</v>
       </c>
       <c r="F127">
-        <v>136831015.91763496</v>
+        <v>173531553</v>
       </c>
       <c r="G127">
-        <v>-32570304.26731844</v>
+        <v>-20063519.938669268</v>
       </c>
       <c r="H127">
-        <v>20880123.841548815</v>
+        <v>146427524.39938018</v>
       </c>
       <c r="I127">
-        <v>121699370.94631772</v>
+        <v>-34854590.46557695</v>
+      </c>
+      <c r="J127">
+        <v>22344530.753984</v>
+      </c>
+      <c r="K127">
+        <v>130234636.4172136</v>
       </c>
     </row>
     <row r="128">
@@ -5082,16 +5850,22 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>520596456</v>
+        <v>557107976</v>
       </c>
       <c r="C128">
-        <v>189907621.64008912</v>
-      </c>
-      <c r="E128">
-        <v>189907623</v>
+        <v>557107975.4977268</v>
+      </c>
+      <c r="D128">
+        <v>203226605.56778425</v>
       </c>
       <c r="F128">
-        <v>76631353.00893886</v>
+        <v>203226608</v>
+      </c>
+      <c r="G128">
+        <v>203226607.02307114</v>
+      </c>
+      <c r="H128">
+        <v>82005817.44732732</v>
       </c>
     </row>
     <row r="129">
@@ -5099,28 +5873,34 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>1067348940</v>
+        <v>702654985</v>
       </c>
       <c r="C129">
-        <v>520596456.30588496</v>
-      </c>
-      <c r="E129">
-        <v>153796234</v>
+        <v>1142206406.247692</v>
+      </c>
+      <c r="D129">
+        <v>557107975.8250648</v>
       </c>
       <c r="F129">
-        <v>189907621.64008912</v>
+        <v>347714944</v>
+      </c>
+      <c r="G129">
+        <v>164582581.33611777</v>
+      </c>
+      <c r="H129">
+        <v>203226605.56778425</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5131,6 +5911,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5138,27 +5920,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5172,16 +5960,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>206854994</v>
+        <v>381845747.8100932</v>
       </c>
       <c r="C3">
-        <v>446938608.59862256</v>
+        <v>221362565.18990678</v>
+      </c>
+      <c r="D3">
+        <v>478284207.5439514</v>
       </c>
       <c r="E3">
-        <v>93439188</v>
+        <v>301409242.5850347</v>
       </c>
       <c r="F3">
-        <v>350310589.46482533</v>
+        <v>296136658.615278</v>
+      </c>
+      <c r="G3">
+        <v>99992453.38472202</v>
+      </c>
+      <c r="H3">
+        <v>374879277.49581945</v>
       </c>
     </row>
     <row r="4">
@@ -5189,16 +5986,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>233879775</v>
+        <v>193386516.42218247</v>
       </c>
       <c r="C4">
-        <v>398451962.308321</v>
+        <v>250282702.57781753</v>
+      </c>
+      <c r="D4">
+        <v>426396998.0899856</v>
       </c>
       <c r="E4">
-        <v>262988435</v>
+        <v>123832020.22456515</v>
       </c>
       <c r="F4">
-        <v>292003713.6428692</v>
+        <v>190687493.23385328</v>
+      </c>
+      <c r="G4">
+        <v>281432869.7661467</v>
+      </c>
+      <c r="H4">
+        <v>312483106.38787144</v>
       </c>
     </row>
     <row r="5">
@@ -5206,10 +6012,16 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>125511785</v>
-      </c>
-      <c r="E5">
-        <v>57417891</v>
+        <v>164336024.62582174</v>
+      </c>
+      <c r="C5">
+        <v>134314430.37417826</v>
+      </c>
+      <c r="F5">
+        <v>71199709.788579</v>
+      </c>
+      <c r="G5">
+        <v>61444838.211421</v>
       </c>
     </row>
     <row r="6">
@@ -5217,16 +6029,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>82636625</v>
+        <v>126782265.72751464</v>
       </c>
       <c r="C6">
-        <v>26528455.25478831</v>
+        <v>88432263.27248536</v>
+      </c>
+      <c r="D6">
+        <v>28389002.325588524</v>
       </c>
       <c r="E6">
-        <v>53093035</v>
+        <v>96799128.31001839</v>
       </c>
       <c r="F6">
-        <v>42831474.96551651</v>
+        <v>84771243.30285719</v>
+      </c>
+      <c r="G6">
+        <v>56816662.69714282</v>
+      </c>
+      <c r="H6">
+        <v>45835418.26035878</v>
       </c>
     </row>
     <row r="7">
@@ -5234,16 +6055,25 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>-1159264</v>
+        <v>5074219.838416858</v>
       </c>
       <c r="C7">
-        <v>-4139872.335966988</v>
+        <v>-1240567.8384168579</v>
+      </c>
+      <c r="D7">
+        <v>-4430218.2032326665</v>
       </c>
       <c r="E7">
-        <v>-1024383</v>
+        <v>-1636516.9052630954</v>
       </c>
       <c r="F7">
-        <v>9469442.003241658</v>
+        <v>3004662.0923801446</v>
+      </c>
+      <c r="G7">
+        <v>-1096227.0923801446</v>
+      </c>
+      <c r="H7">
+        <v>10133571.987895168</v>
       </c>
     </row>
     <row r="8">
@@ -5251,16 +6081,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>5613784</v>
+        <v>5517574.79042294</v>
       </c>
       <c r="C8">
-        <v>58929727.2712675</v>
+        <v>6007501.20957706</v>
+      </c>
+      <c r="D8">
+        <v>63062705.629961155</v>
       </c>
       <c r="E8">
-        <v>10681598</v>
+        <v>-3585787.128411567</v>
       </c>
       <c r="F8">
-        <v>66075554.61969398</v>
+        <v>3322269.648851486</v>
+      </c>
+      <c r="G8">
+        <v>11430741.351148514</v>
+      </c>
+      <c r="H8">
+        <v>70709698.53868383</v>
       </c>
     </row>
     <row r="9">
@@ -5283,16 +6122,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-17912</v>
+        <v>1145359.2404713014</v>
       </c>
       <c r="C12">
-        <v>2208326.5563501418</v>
+        <v>-19168.240471301408</v>
+      </c>
+      <c r="D12">
+        <v>2363205.3635149896</v>
       </c>
       <c r="E12">
-        <v>-14607566</v>
+        <v>-7704333.185301229</v>
       </c>
       <c r="F12">
-        <v>-4458287.204235099</v>
+        <v>-24758708.75142885</v>
+      </c>
+      <c r="G12">
+        <v>-15632053.24857115</v>
+      </c>
+      <c r="H12">
+        <v>-4770964.784552503</v>
       </c>
     </row>
     <row r="13">
@@ -5310,16 +6158,25 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
-        <v>-8164</v>
+        <v>-27005.425903991476</v>
       </c>
       <c r="C15">
-        <v>5949.500267146679</v>
+        <v>-8736.574096008526</v>
+      </c>
+      <c r="D15">
+        <v>6366.762606338714</v>
       </c>
       <c r="E15">
-        <v>3119</v>
+        <v>-120491.97544858966</v>
       </c>
       <c r="F15">
-        <v>76572.7819823235</v>
+        <v>-240983.74799184842</v>
+      </c>
+      <c r="G15">
+        <v>3337.747991848431</v>
+      </c>
+      <c r="H15">
+        <v>81943.13859947032</v>
       </c>
     </row>
     <row r="16">
@@ -5357,16 +6214,25 @@
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B22">
+        <v>-97748</v>
+      </c>
+      <c r="C22">
         <v>0</v>
       </c>
-      <c r="C22">
-        <v>-41265.540002385125</v>
+      <c r="D22">
+        <v>-44159.657991504355</v>
       </c>
       <c r="E22">
-        <v>-168172</v>
+        <v>1.310989480902208</v>
       </c>
       <c r="F22">
-        <v>0.1563562587762135</v>
+        <v>-2009.4224799184594</v>
+      </c>
+      <c r="G22">
+        <v>-179966.57752008154</v>
+      </c>
+      <c r="H22">
+        <v>0.1673221509263385</v>
       </c>
     </row>
     <row r="23">
@@ -5399,10 +6265,16 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-98981789</v>
-      </c>
-      <c r="E28">
-        <v>-166301058</v>
+        <v>25377886.24473071</v>
+      </c>
+      <c r="C28">
+        <v>-105923779.24473071</v>
+      </c>
+      <c r="F28">
+        <v>34507826.84635121</v>
+      </c>
+      <c r="G28">
+        <v>-177964418.8463512</v>
       </c>
     </row>
     <row r="29">
@@ -5420,16 +6292,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-45767992</v>
+        <v>77326498.02370474</v>
       </c>
       <c r="C31">
-        <v>-72981906.60733011</v>
+        <v>-48977885.02370473</v>
+      </c>
+      <c r="D31">
+        <v>-78100420.71814229</v>
       </c>
       <c r="E31">
-        <v>-102392229</v>
+        <v>76268472.6472461</v>
       </c>
       <c r="F31">
-        <v>-66269674.872656345</v>
+        <v>42952219.09382324</v>
+      </c>
+      <c r="G31">
+        <v>-109573407.09382324</v>
+      </c>
+      <c r="H31">
+        <v>-70917433.224321</v>
       </c>
     </row>
     <row r="32">
@@ -5442,16 +6323,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1074110</v>
+        <v>1360057.6465291176</v>
       </c>
       <c r="C33">
-        <v>1956645.2444537515</v>
+        <v>-1149441.6465291176</v>
+      </c>
+      <c r="D33">
+        <v>2093872.6307904106</v>
       </c>
       <c r="E33">
-        <v>-3518656</v>
+        <v>-950412.5473951809</v>
       </c>
       <c r="F33">
-        <v>-540111.3500218374</v>
+        <v>-3665125.528372737</v>
+      </c>
+      <c r="G33">
+        <v>-3765433.471627263</v>
+      </c>
+      <c r="H33">
+        <v>-577991.5273837552</v>
       </c>
     </row>
     <row r="34">
@@ -5459,10 +6349,16 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B34">
-        <v>-79088702</v>
-      </c>
-      <c r="E34">
-        <v>-56235603</v>
+        <v>-54179591.81135012</v>
+      </c>
+      <c r="C34">
+        <v>-84635510.18864988</v>
+      </c>
+      <c r="F34">
+        <v>-3374586.3925503045</v>
+      </c>
+      <c r="G34">
+        <v>-60179631.607449695</v>
       </c>
     </row>
     <row r="35">
@@ -5480,16 +6376,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>55553</v>
+        <v>12337.845081386382</v>
       </c>
       <c r="C37">
-        <v>11396.864539998118</v>
+        <v>59449.15491861362</v>
+      </c>
+      <c r="D37">
+        <v>12196.172405177073</v>
       </c>
       <c r="E37">
-        <v>-154128</v>
+        <v>12470.807027755829</v>
       </c>
       <c r="F37">
-        <v>44224.19470130495</v>
+        <v>14042.615417638648</v>
+      </c>
+      <c r="G37">
+        <v>-164937.61541763865</v>
+      </c>
+      <c r="H37">
+        <v>47325.815022569615</v>
       </c>
     </row>
     <row r="38">
@@ -5502,16 +6407,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-8983772</v>
+        <v>3949456.9975069445</v>
       </c>
       <c r="C39">
-        <v>-709545.7662145845</v>
+        <v>-9613839.997506944</v>
+      </c>
+      <c r="D39">
+        <v>-759309.059412403</v>
       </c>
       <c r="E39">
-        <v>-8339759</v>
+        <v>2678234.555250325</v>
       </c>
       <c r="F39">
-        <v>-860890.5087075885</v>
+        <v>4021429.7802981343</v>
+      </c>
+      <c r="G39">
+        <v>-8924659.780298134</v>
+      </c>
+      <c r="H39">
+        <v>-921268.2163001373</v>
       </c>
     </row>
     <row r="40">
@@ -5519,16 +6433,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>8228277</v>
+        <v>-4851874.10007138</v>
       </c>
       <c r="C40">
-        <v>-4543097.1748552825</v>
+        <v>8805359.10007138</v>
+      </c>
+      <c r="D40">
+        <v>-4861722.818898845</v>
       </c>
       <c r="E40">
-        <v>-468011</v>
+        <v>1824824.0076650754</v>
       </c>
       <c r="F40">
-        <v>7597316.042887301</v>
+        <v>-6837034.509646369</v>
+      </c>
+      <c r="G40">
+        <v>-500834.4903536313</v>
+      </c>
+      <c r="H40">
+        <v>8130146.317917588</v>
       </c>
     </row>
     <row r="41">
@@ -5541,16 +6464,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>3725111</v>
+        <v>-7343293.989632094</v>
       </c>
       <c r="C42">
-        <v>61842167.36842308</v>
+        <v>3986367.989632094</v>
+      </c>
+      <c r="D42">
+        <v>66179406.8437027</v>
       </c>
       <c r="E42">
-        <v>-3165809</v>
+        <v>-62019317.82830942</v>
       </c>
       <c r="F42">
-        <v>51911899.42400619</v>
+        <v>130057.89494251041</v>
+      </c>
+      <c r="G42">
+        <v>-3387839.8949425104</v>
+      </c>
+      <c r="H42">
+        <v>55552689.34129989</v>
       </c>
     </row>
     <row r="43">
@@ -5558,16 +6490,25 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B43">
-        <v>21016045</v>
+        <v>19510341.391039994</v>
       </c>
       <c r="C43">
-        <v>67979982.48270154</v>
+        <v>22489984.608960006</v>
+      </c>
+      <c r="D43">
+        <v>72747691.57343012</v>
       </c>
       <c r="E43">
-        <v>18177684</v>
+        <v>-56585138.48066061</v>
       </c>
       <c r="F43">
-        <v>56574101.9435896</v>
+        <v>2237991.043137111</v>
+      </c>
+      <c r="G43">
+        <v>19452557.95686289</v>
+      </c>
+      <c r="H43">
+        <v>60541870.840924844</v>
       </c>
     </row>
     <row r="44">
@@ -5590,16 +6531,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>4933553</v>
+        <v>4318914.121376146</v>
       </c>
       <c r="C47">
-        <v>4788249.386758357</v>
+        <v>5279562.878623854</v>
+      </c>
+      <c r="D47">
+        <v>5124068.539635199</v>
       </c>
       <c r="E47">
-        <v>-2315604</v>
+        <v>3600071.181057371</v>
       </c>
       <c r="F47">
-        <v>-1893829.150219902</v>
+        <v>123814.60497473367</v>
+      </c>
+      <c r="G47">
+        <v>-2478006.6049747337</v>
+      </c>
+      <c r="H47">
+        <v>-2026650.9916801858</v>
       </c>
     </row>
     <row r="48">
@@ -5607,16 +6557,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-2025752</v>
+        <v>-14724959.87945401</v>
       </c>
       <c r="C48">
-        <v>-3697781.91828023</v>
+        <v>-2167826.12054599</v>
+      </c>
+      <c r="D48">
+        <v>-3957122.2096932596</v>
       </c>
       <c r="E48">
-        <v>-7888943</v>
+        <v>19863992.95141393</v>
       </c>
       <c r="F48">
-        <v>10941947.35917331</v>
+        <v>-1094981.755672736</v>
+      </c>
+      <c r="G48">
+        <v>-8442226.244327264</v>
+      </c>
+      <c r="H48">
+        <v>11709350.056105148</v>
       </c>
     </row>
     <row r="49">
@@ -5624,10 +6583,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>260409771</v>
-      </c>
-      <c r="E49">
-        <v>154105268</v>
+        <v>383100427.2927349</v>
+      </c>
+      <c r="C49">
+        <v>278673353.7072651</v>
+      </c>
+      <c r="F49">
+        <v>296395029.8687835</v>
+      </c>
+      <c r="G49">
+        <v>164913289.1312165</v>
       </c>
     </row>
     <row r="50">
@@ -5695,16 +6660,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-53554777</v>
+        <v>-1254679.4826417044</v>
       </c>
       <c r="C62">
-        <v>-59563412.39251527</v>
+        <v>-57310788.517358296</v>
+      </c>
+      <c r="D62">
+        <v>-63740833.6328175</v>
       </c>
       <c r="E62">
-        <v>-60666080</v>
+        <v>62306732.33732278</v>
       </c>
       <c r="F62">
-        <v>-48502129.522746444</v>
+        <v>-258371.25350552797</v>
+      </c>
+      <c r="G62">
+        <v>-64920835.74649447</v>
+      </c>
+      <c r="H62">
+        <v>-51903778.58766254</v>
       </c>
     </row>
     <row r="63">
@@ -5728,16 +6702,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-128926267</v>
+        <v>-125574152.2950418</v>
       </c>
       <c r="C67">
-        <v>82372321.73377609</v>
+        <v>-137968383.7049582</v>
+      </c>
+      <c r="D67">
+        <v>88149423.35710287</v>
       </c>
       <c r="E67">
-        <v>-100374754</v>
+        <v>-382661011.69923854</v>
       </c>
       <c r="F67">
-        <v>-166464620.35391578</v>
+        <v>-93474479.52748309</v>
+      </c>
+      <c r="G67">
+        <v>-107414438.47251691</v>
+      </c>
+      <c r="H67">
+        <v>-178139452.48480088</v>
       </c>
     </row>
     <row r="68">
@@ -5790,16 +6773,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
+        <v>174506</v>
+      </c>
+      <c r="C77">
         <v>0</v>
       </c>
-      <c r="C77">
-        <v>354181333.1817247</v>
+      <c r="D77">
+        <v>379021492.0094587</v>
       </c>
       <c r="E77">
-        <v>296746</v>
+        <v>-376811968.37454337</v>
       </c>
       <c r="F77">
-        <v>276518512.9561384</v>
+        <v>2009.0116739164805</v>
+      </c>
+      <c r="G77">
+        <v>317557.9883260835</v>
+      </c>
+      <c r="H77">
+        <v>295911866.4085493</v>
       </c>
     </row>
     <row r="78">
@@ -5807,16 +6799,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-131830300</v>
+        <v>-128052714.80193132</v>
       </c>
       <c r="C78">
-        <v>-520852089.3947584</v>
+        <v>-141076088.19806868</v>
+      </c>
+      <c r="D78">
+        <v>-557381537.488751</v>
       </c>
       <c r="E78">
-        <v>-117700130</v>
+        <v>247387408.92606363</v>
       </c>
       <c r="F78">
-        <v>-436734117.82230306</v>
+        <v>-121112929.35242088</v>
+      </c>
+      <c r="G78">
+        <v>-125954912.64757912</v>
+      </c>
+      <c r="H78">
+        <v>-467364034.8615223</v>
       </c>
     </row>
     <row r="79">
@@ -5899,10 +6900,16 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B94">
-        <v>2904033</v>
-      </c>
-      <c r="E94">
-        <v>17028630</v>
+        <v>2304056.506889524</v>
+      </c>
+      <c r="C94">
+        <v>3107704.493110476</v>
+      </c>
+      <c r="F94">
+        <v>27636440.813263886</v>
+      </c>
+      <c r="G94">
+        <v>18222916.186736114</v>
       </c>
     </row>
     <row r="95">
@@ -5936,16 +6943,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>516332219</v>
+        <v>-662643456.4372858</v>
       </c>
       <c r="C101">
-        <v>-12121166.878356695</v>
+        <v>552544670.4372858</v>
+      </c>
+      <c r="D101">
+        <v>-12971272.974381149</v>
       </c>
       <c r="E101">
-        <v>-11813039</v>
+        <v>-243896594.3425259</v>
       </c>
       <c r="F101">
-        <v>-14444648.92595622</v>
+        <v>-9067106.149125619</v>
+      </c>
+      <c r="G101">
+        <v>-12641534.850874381</v>
+      </c>
+      <c r="H101">
+        <v>-15457710.14606154</v>
       </c>
     </row>
     <row r="102">
@@ -5963,9 +6979,15 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>525203079</v>
-      </c>
-      <c r="E104">
+        <v>-35976642.46292496</v>
+      </c>
+      <c r="C104">
+        <v>562037679.462925</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
         <v>0</v>
       </c>
     </row>
@@ -5996,11 +7018,17 @@
       <c r="B109">
         <v>0</v>
       </c>
-      <c r="E109">
+      <c r="C109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>6179790.750200734</v>
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>6613204.285516515</v>
       </c>
     </row>
     <row r="110">
@@ -6011,13 +7039,22 @@
         <v>0</v>
       </c>
       <c r="C110">
-        <v>28745868.863184724</v>
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>30761932.05259158</v>
       </c>
       <c r="E110">
-        <v>-3271697</v>
+        <v>-30403163.69621528</v>
       </c>
       <c r="F110">
-        <v>12258555.404436186</v>
+        <v>198388.24549103435</v>
+      </c>
+      <c r="G110">
+        <v>-3501154.2454910344</v>
+      </c>
+      <c r="H110">
+        <v>13118297.109368265</v>
       </c>
     </row>
     <row r="111">
@@ -6035,10 +7072,16 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
-        <v>-10144374</v>
-      </c>
-      <c r="E113">
-        <v>-8409981</v>
+        <v>-10780610.32476453</v>
+      </c>
+      <c r="C113">
+        <v>-10855839.67523547</v>
+      </c>
+      <c r="F113">
+        <v>-10612530.268921623</v>
+      </c>
+      <c r="G113">
+        <v>-8999806.731078377</v>
       </c>
     </row>
     <row r="114">
@@ -6060,11 +7103,14 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="C117">
-        <v>5.067911446094513</v>
-      </c>
-      <c r="F117">
-        <v>169225925.12004784</v>
+      <c r="D117">
+        <v>5.423344433307648</v>
+      </c>
+      <c r="E117">
+        <v>-233321425.5336331</v>
+      </c>
+      <c r="H117">
+        <v>181094418.6399912</v>
       </c>
     </row>
     <row r="118">
@@ -6072,10 +7118,16 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-65190</v>
-      </c>
-      <c r="E118">
-        <v>-131361</v>
+        <v>-262837.96358172514</v>
+      </c>
+      <c r="C118">
+        <v>-69762.03641827483</v>
+      </c>
+      <c r="F118">
+        <v>-195089.1256950299</v>
+      </c>
+      <c r="G118">
+        <v>-140573.8743049701</v>
       </c>
     </row>
     <row r="119">
@@ -6103,16 +7155,25 @@
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
       <c r="B123">
-        <v>1338704</v>
+        <v>679597.3139854241</v>
       </c>
       <c r="C123">
-        <v>-2124220.279435592</v>
+        <v>1432592.686014576</v>
+      </c>
+      <c r="D123">
+        <v>-2273200.3757389737</v>
       </c>
       <c r="E123">
+        <v>732924.2062591696</v>
+      </c>
+      <c r="F123">
+        <v>1542125</v>
+      </c>
+      <c r="G123">
         <v>0</v>
       </c>
-      <c r="F123">
-        <v>-2373827.709720091</v>
+      <c r="H123">
+        <v>-2540313.7772082053</v>
       </c>
     </row>
     <row r="124">
@@ -6125,10 +7186,16 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>594260946</v>
-      </c>
-      <c r="E125">
-        <v>-18748605</v>
+        <v>-406371860.9222343</v>
+      </c>
+      <c r="C125">
+        <v>635938851.9222343</v>
+      </c>
+      <c r="F125">
+        <v>193595072.93866926</v>
+      </c>
+      <c r="G125">
+        <v>-20063519.938669268</v>
       </c>
     </row>
     <row r="126">
@@ -6141,16 +7208,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>594260946</v>
+        <v>-406371860.9222343</v>
       </c>
       <c r="C127">
-        <v>517189763.4540422</v>
+        <v>635938851.9222343</v>
+      </c>
+      <c r="D127">
+        <v>553462357.9266734</v>
       </c>
       <c r="E127">
-        <v>-18748605</v>
+        <v>-325148363.4567299</v>
       </c>
       <c r="F127">
-        <v>169401320.1849534</v>
+        <v>193595072.93866926</v>
+      </c>
+      <c r="G127">
+        <v>-20063519.938669268</v>
+      </c>
+      <c r="H127">
+        <v>181282114.86495712</v>
       </c>
     </row>
     <row r="128">
@@ -6158,10 +7234,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>520596456</v>
-      </c>
-      <c r="E128">
-        <v>189907623</v>
+        <v>0.5022732019424438</v>
+      </c>
+      <c r="C128">
+        <v>557107975.4977268</v>
+      </c>
+      <c r="F128">
+        <v>0.9769288599491119</v>
+      </c>
+      <c r="G128">
+        <v>203226607.02307114</v>
       </c>
     </row>
     <row r="129">
@@ -6169,22 +7251,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>1067348940</v>
-      </c>
-      <c r="E129">
-        <v>153796234</v>
+        <v>-439551421.2476921</v>
+      </c>
+      <c r="C129">
+        <v>1142206406.247692</v>
+      </c>
+      <c r="F129">
+        <v>183132362.66388223</v>
+      </c>
+      <c r="G129">
+        <v>164582581.33611777</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6195,6 +7283,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6202,27 +7292,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -6236,22 +7332,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>1212177779.7130969</v>
+        <v>1382901763.1289861</v>
       </c>
       <c r="C3">
-        <v>1098761973.7130969</v>
+        <v>1297192673.934171</v>
       </c>
       <c r="D3">
-        <v>1002133954.5792997</v>
-      </c>
-      <c r="F3">
-        <v>691390792.4809455</v>
+        <v>1175822562.1289861</v>
+      </c>
+      <c r="E3">
+        <v>1072417632.0808542</v>
       </c>
       <c r="H3">
-        <v>323958688.4400544</v>
-      </c>
-      <c r="I3">
-        <v>543298975.7907176</v>
+        <v>739880804.4840561</v>
+      </c>
+      <c r="J3">
+        <v>346679211.85721165</v>
+      </c>
+      <c r="K3">
+        <v>581402714.1451674</v>
       </c>
     </row>
     <row r="4">
@@ -6259,22 +7358,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>926238396.7902853</v>
+        <v>993898237.3145508</v>
       </c>
       <c r="C4">
-        <v>955347056.7902853</v>
+        <v>991199214.1262215</v>
       </c>
       <c r="D4">
-        <v>848898808.1248336</v>
-      </c>
-      <c r="F4">
-        <v>668832960.438582</v>
+        <v>1022349381.3145508</v>
+      </c>
+      <c r="E4">
+        <v>908435489.6124365</v>
       </c>
       <c r="H4">
-        <v>306145506.7014332</v>
-      </c>
-      <c r="I4">
-        <v>315883338.38153726</v>
+        <v>715740901.1176397</v>
+      </c>
+      <c r="J4">
+        <v>327616720.16868514</v>
+      </c>
+      <c r="K4">
+        <v>338037505.07898504</v>
       </c>
     </row>
     <row r="5">
@@ -6282,13 +7384,16 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>340393732.0969074</v>
+        <v>457403225.9447276</v>
       </c>
       <c r="C5">
-        <v>272299838.0969074</v>
-      </c>
-      <c r="F5">
-        <v>262394013.8437791</v>
+        <v>364266911.1074848</v>
+      </c>
+      <c r="D5">
+        <v>291397318.9447276</v>
+      </c>
+      <c r="H5">
+        <v>280796759.4678176</v>
       </c>
     </row>
     <row r="6">
@@ -6296,22 +7401,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>278835765.53229916</v>
+        <v>340402659.6356069</v>
       </c>
       <c r="C6">
-        <v>249292175.53229913</v>
+        <v>298391637.2109495</v>
       </c>
       <c r="D6">
-        <v>265595195.24302733</v>
-      </c>
-      <c r="F6">
-        <v>216135364.49310306</v>
+        <v>266776036.6356069</v>
+      </c>
+      <c r="E6">
+        <v>284222452.5703772</v>
       </c>
       <c r="H6">
-        <v>227972426.51804158</v>
-      </c>
-      <c r="I6">
-        <v>250206367.5504006</v>
+        <v>231293805.32359198</v>
+      </c>
+      <c r="J6">
+        <v>243961048.03058904</v>
+      </c>
+      <c r="K6">
+        <v>267754344.6101443</v>
       </c>
     </row>
     <row r="7">
@@ -6319,22 +7427,25 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>-4020656.1004789593</v>
+        <v>-2233083.1084957616</v>
       </c>
       <c r="C7">
-        <v>-3885775.1004789593</v>
+        <v>-4302640.854532475</v>
       </c>
       <c r="D7">
-        <v>9723539.238729687</v>
-      </c>
-      <c r="F7">
-        <v>12604467.35618563</v>
+        <v>-4158300.1084957616</v>
+      </c>
+      <c r="E7">
+        <v>10405490.082632072</v>
       </c>
       <c r="H7">
-        <v>1922666.249267942</v>
-      </c>
-      <c r="I7">
-        <v>3999688.8292300473</v>
+        <v>13488469.255026512</v>
+      </c>
+      <c r="J7">
+        <v>2057510.552256758</v>
+      </c>
+      <c r="K7">
+        <v>4280203.064373579</v>
       </c>
     </row>
     <row r="8">
@@ -6342,22 +7453,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>64297264.094801456</v>
+        <v>71001994.50154959</v>
       </c>
       <c r="C8">
-        <v>69365078.09480146</v>
+        <v>68806689.35997812</v>
       </c>
       <c r="D8">
-        <v>76510905.44322793</v>
-      </c>
-      <c r="F8">
-        <v>82730220.99075378</v>
+        <v>74229929.50154959</v>
+      </c>
+      <c r="E8">
+        <v>81876922.41027227</v>
       </c>
       <c r="H8">
-        <v>56226437.42086944</v>
-      </c>
-      <c r="I8">
-        <v>55893049.05990699</v>
+        <v>88532423.5258305</v>
+      </c>
+      <c r="J8">
+        <v>60169823.20945766</v>
+      </c>
+      <c r="K8">
+        <v>59813052.984286755</v>
       </c>
     </row>
     <row r="9">
@@ -6380,22 +7494,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-28145077.53231053</v>
+        <v>-4214936.82178624</v>
       </c>
       <c r="C12">
-        <v>-42734731.53231053</v>
+        <v>-30119004.81368639</v>
       </c>
       <c r="D12">
-        <v>-49401345.29289577</v>
-      </c>
-      <c r="F12">
-        <v>-7624876.047429188</v>
+        <v>-45731889.82178624</v>
+      </c>
+      <c r="E12">
+        <v>-52866059.96985373</v>
       </c>
       <c r="H12">
-        <v>60075808.65895308</v>
-      </c>
-      <c r="I12">
-        <v>70308454.26035722</v>
+        <v>-8159639.21622314</v>
+      </c>
+      <c r="J12">
+        <v>64289166.30653774</v>
+      </c>
+      <c r="K12">
+        <v>75239468.4249678</v>
       </c>
     </row>
     <row r="13">
@@ -6413,22 +7530,25 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
-        <v>-339999.9719027739</v>
+        <v>-149867.21284225094</v>
       </c>
       <c r="C15">
-        <v>-328716.9719027739</v>
+        <v>-363845.53493010794</v>
       </c>
       <c r="D15">
-        <v>-258093.69018759707</v>
-      </c>
-      <c r="F15">
-        <v>140541.50148981038</v>
+        <v>-351771.21284225094</v>
+      </c>
+      <c r="E15">
+        <v>-276194.83684911934</v>
       </c>
       <c r="H15">
-        <v>-751558.0986867505</v>
-      </c>
-      <c r="I15">
-        <v>47592563.09982122</v>
+        <v>150398.24122121764</v>
+      </c>
+      <c r="J15">
+        <v>-804267.8854277417</v>
+      </c>
+      <c r="K15">
+        <v>50930420.6198615</v>
       </c>
     </row>
     <row r="16">
@@ -6455,8 +7575,8 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="I20">
-        <v>-12815663.566122796</v>
+      <c r="K20">
+        <v>-13714477.503055936</v>
       </c>
     </row>
     <row r="21">
@@ -6469,22 +7589,25 @@
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B22">
-        <v>-43142.04468577381</v>
+        <v>-141906.34700202345</v>
       </c>
       <c r="C22">
-        <v>-211314.0446857738</v>
+        <v>-46167.76948194191</v>
       </c>
       <c r="D22">
-        <v>-170048.3483271299</v>
-      </c>
-      <c r="F22">
-        <v>-52816.95674000461</v>
+        <v>-226134.34700202345</v>
+      </c>
+      <c r="E22">
+        <v>-181974.52168836817</v>
       </c>
       <c r="H22">
-        <v>-37247.812331834575</v>
-      </c>
-      <c r="I22">
-        <v>-32110.103848278402</v>
+        <v>-56521.22196040264</v>
+      </c>
+      <c r="J22">
+        <v>-39860.150949447925</v>
+      </c>
+      <c r="K22">
+        <v>-34362.11434358314</v>
       </c>
     </row>
     <row r="23">
@@ -6517,13 +7640,16 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>681979.7864548266</v>
+        <v>-8400130.834797546</v>
       </c>
       <c r="C28">
-        <v>-66637289.21354518</v>
-      </c>
-      <c r="F28">
-        <v>-189900687.8808038</v>
+        <v>729809.766822949</v>
+      </c>
+      <c r="D28">
+        <v>-71310829.83479755</v>
+      </c>
+      <c r="H28">
+        <v>-203219185.5161233</v>
       </c>
     </row>
     <row r="29">
@@ -6541,22 +7667,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-7342644.839658268</v>
+        <v>26516664.929103807</v>
       </c>
       <c r="C31">
-        <v>-63966881.83965827</v>
+        <v>-7857614.000777684</v>
       </c>
       <c r="D31">
-        <v>-57254650.1049845</v>
-      </c>
-      <c r="F31">
-        <v>-134160787.91254087</v>
+        <v>-68453136.0708962</v>
+      </c>
+      <c r="E31">
+        <v>-61270148.5770749</v>
       </c>
       <c r="H31">
-        <v>-84985304.97447746</v>
-      </c>
-      <c r="I31">
-        <v>50272691.104305625</v>
+        <v>-143570022.58412522</v>
+      </c>
+      <c r="J31">
+        <v>-90945665.60281776</v>
+      </c>
+      <c r="K31">
+        <v>53798516.76120955</v>
       </c>
     </row>
     <row r="32">
@@ -6569,22 +7698,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-3430511.5444225315</v>
+        <v>1354076.0833952297</v>
       </c>
       <c r="C33">
-        <v>-5875057.5444225315</v>
+        <v>-3671107.091506625</v>
       </c>
       <c r="D33">
-        <v>-8371814.13889812</v>
-      </c>
-      <c r="F33">
-        <v>-824849.9524000604</v>
+        <v>-6287098.91660477</v>
+      </c>
+      <c r="E33">
+        <v>-8958963.074778937</v>
       </c>
       <c r="H33">
-        <v>190393.78434435528</v>
-      </c>
-      <c r="I33">
-        <v>346108.6105986541</v>
+        <v>-882699.9910867506</v>
+      </c>
+      <c r="J33">
+        <v>203746.86481429788</v>
+      </c>
+      <c r="K33">
+        <v>370382.5969820802</v>
       </c>
     </row>
     <row r="34">
@@ -6592,13 +7724,16 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B34">
-        <v>-55167102.299495995</v>
+        <v>-109841198.08190969</v>
       </c>
       <c r="C34">
-        <v>-32314003.299496</v>
-      </c>
-      <c r="F34">
-        <v>-26602171.356532827</v>
+        <v>-59036192.663109876</v>
+      </c>
+      <c r="D34">
+        <v>-34580314.081909694</v>
+      </c>
+      <c r="H34">
+        <v>-28467888.43349641</v>
       </c>
     </row>
     <row r="35">
@@ -6616,22 +7751,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>91725.66091801916</v>
+        <v>96453.9794329329</v>
       </c>
       <c r="C37">
-        <v>-117955.33908198084</v>
+        <v>98158.74976918517</v>
       </c>
       <c r="D37">
-        <v>-85128.00892067401</v>
-      </c>
-      <c r="F37">
-        <v>364047.12197662407</v>
+        <v>-126228.0205670671</v>
+      </c>
+      <c r="E37">
+        <v>-91098.37794967456</v>
       </c>
       <c r="H37">
-        <v>162379.83743859918</v>
-      </c>
-      <c r="I37">
-        <v>193984.66821294717</v>
+        <v>389579.2081807239</v>
+      </c>
+      <c r="J37">
+        <v>173768.18734445627</v>
+      </c>
+      <c r="K37">
+        <v>207589.59178491458</v>
       </c>
     </row>
     <row r="38">
@@ -6644,22 +7782,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-3432733.3501324747</v>
+        <v>-3745457.5041620783</v>
       </c>
       <c r="C39">
-        <v>-2788720.350132475</v>
+        <v>-3673484.721370889</v>
       </c>
       <c r="D39">
-        <v>-2940065.092625479</v>
-      </c>
-      <c r="F39">
-        <v>-2868996.1380813746</v>
+        <v>-2984304.5041620783</v>
+      </c>
+      <c r="E39">
+        <v>-3146263.6610498126</v>
       </c>
       <c r="H39">
-        <v>-610946.3439513901</v>
-      </c>
-      <c r="I39">
-        <v>1821253.3499385251</v>
+        <v>-3070210.3554030177</v>
+      </c>
+      <c r="J39">
+        <v>-653794.463818818</v>
+      </c>
+      <c r="K39">
+        <v>1948985.1591550305</v>
       </c>
     </row>
     <row r="40">
@@ -6667,22 +7808,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-998542.4312567059</v>
+        <v>916586.1887662299</v>
       </c>
       <c r="C40">
-        <v>-9694830.431256706</v>
+        <v>-1068574.2208087593</v>
       </c>
       <c r="D40">
-        <v>2445582.786485878</v>
-      </c>
-      <c r="F40">
-        <v>5319536.987173686</v>
+        <v>-10374767.81123377</v>
+      </c>
+      <c r="E40">
+        <v>2617101.3255826635</v>
       </c>
       <c r="H40">
-        <v>-1192901.496938127</v>
-      </c>
-      <c r="I40">
-        <v>-3871529.759071281</v>
+        <v>5692617.472427837</v>
+      </c>
+      <c r="J40">
+        <v>-1276564.4680597053</v>
+      </c>
+      <c r="K40">
+        <v>-4143055.684104395</v>
       </c>
     </row>
     <row r="41">
@@ -6695,22 +7839,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>7734091.979395937</v>
+        <v>803163.0153932846</v>
       </c>
       <c r="C42">
-        <v>843171.9793959367</v>
+        <v>8276514.899967888</v>
       </c>
       <c r="D42">
-        <v>-9087095.965020962</v>
-      </c>
-      <c r="F42">
-        <v>2431702.7241588333</v>
+        <v>902307.0153932845</v>
+      </c>
+      <c r="E42">
+        <v>-9724410.487009525</v>
       </c>
       <c r="H42">
-        <v>-61545712.338498816</v>
-      </c>
-      <c r="I42">
-        <v>-43997841.45256325</v>
+        <v>2602247.7987603415</v>
+      </c>
+      <c r="J42">
+        <v>-65862160.232351914</v>
+      </c>
+      <c r="K42">
+        <v>-47083586.71175333</v>
       </c>
     </row>
     <row r="43">
@@ -6718,33 +7865,36 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B43">
-        <v>38210661.63973909</v>
+        <v>58162879.09276951</v>
       </c>
       <c r="C43">
-        <v>35372300.63973909</v>
+        <v>40890528.744866624</v>
       </c>
       <c r="D43">
-        <v>23966420.100627154</v>
-      </c>
-      <c r="F43">
-        <v>-13835860.52897233</v>
+        <v>37853102.09276951</v>
+      </c>
+      <c r="E43">
+        <v>25647281.360264234</v>
       </c>
       <c r="H43">
-        <v>14572627.807491045</v>
-      </c>
-      <c r="I43">
-        <v>76393.84373459412</v>
+        <v>-14806224.974694569</v>
+      </c>
+      <c r="J43">
+        <v>15594664.70035519</v>
+      </c>
+      <c r="K43">
+        <v>81751.65069404437</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="H44">
-        <v>-131925013.92225634</v>
-      </c>
-      <c r="I44">
-        <v>-34434772.24525276</v>
+      <c r="J44">
+        <v>-141177444.7879408</v>
+      </c>
+      <c r="K44">
+        <v>-36849821.06808287</v>
       </c>
     </row>
     <row r="45">
@@ -6762,22 +7912,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>13201633.636750933</v>
+        <v>18322616.72069257</v>
       </c>
       <c r="C47">
-        <v>5952476.636750933</v>
+        <v>14127517.204291157</v>
       </c>
       <c r="D47">
-        <v>-729601.9002273264</v>
-      </c>
-      <c r="F47">
-        <v>-5135099.6504366975</v>
+        <v>6369947.72069257</v>
+      </c>
+      <c r="E47">
+        <v>-780771.8106228148</v>
       </c>
       <c r="H47">
-        <v>-19306178.694341324</v>
-      </c>
-      <c r="I47">
-        <v>23618120.541520897</v>
+        <v>-5495244.804804959</v>
+      </c>
+      <c r="J47">
+        <v>-20660198.514685705</v>
+      </c>
+      <c r="K47">
+        <v>25274554.154759716</v>
       </c>
     </row>
     <row r="48">
@@ -6785,22 +7938,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>11815401.334616818</v>
+        <v>-985915.258279331</v>
       </c>
       <c r="C48">
-        <v>5952210.334616818</v>
+        <v>12644062.86550194</v>
       </c>
       <c r="D48">
-        <v>20591939.61207036</v>
-      </c>
-      <c r="F48">
-        <v>-14588209.175148768</v>
+        <v>6369662.741720668</v>
+      </c>
+      <c r="E48">
+        <v>22036135.007519074</v>
       </c>
       <c r="H48">
-        <v>-79833946.0794899</v>
-      </c>
-      <c r="I48">
-        <v>-178833662.35616323</v>
+        <v>-15611338.851881262</v>
+      </c>
+      <c r="J48">
+        <v>-85433021.22736561</v>
+      </c>
+      <c r="K48">
+        <v>-191375985.0606554</v>
       </c>
     </row>
     <row r="49">
@@ -6808,13 +7964,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>1267314108.6736476</v>
+        <v>1442901332.424481</v>
       </c>
       <c r="C49">
-        <v>1161009605.6736476</v>
-      </c>
-      <c r="F49">
-        <v>741326286.4015572</v>
+        <v>1356195935.0005295</v>
+      </c>
+      <c r="D49">
+        <v>1242435870.424481</v>
+      </c>
+      <c r="H49">
+        <v>793318475.0693339</v>
       </c>
     </row>
     <row r="50">
@@ -6882,22 +8041,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-55136328.96055062</v>
+        <v>-59999569.29549472</v>
       </c>
       <c r="C62">
-        <v>-62247631.96055062</v>
+        <v>-59003261.066358544</v>
       </c>
       <c r="D62">
-        <v>-51186349.09078179</v>
-      </c>
-      <c r="F62">
-        <v>-49935493.92061175</v>
+        <v>-66613308.29549472</v>
+      </c>
+      <c r="E62">
+        <v>-54776253.25033976</v>
       </c>
       <c r="H62">
-        <v>-892130.8095936707</v>
-      </c>
-      <c r="I62">
-        <v>1488429.976140555</v>
+        <v>-53437670.58527778</v>
+      </c>
+      <c r="J62">
+        <v>-954699.5249077874</v>
+      </c>
+      <c r="K62">
+        <v>1592819.5459667025</v>
       </c>
     </row>
     <row r="63">
@@ -6921,22 +8083,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-491484659.25752234</v>
+        <v>-558054124.3421357</v>
       </c>
       <c r="C67">
-        <v>-462933146.25752234</v>
+        <v>-525954451.574577</v>
       </c>
       <c r="D67">
-        <v>-711770088.3452142</v>
-      </c>
-      <c r="F67">
-        <v>-428780641.4426715</v>
+        <v>-495400506.34213567</v>
+      </c>
+      <c r="E67">
+        <v>-761689382.1840394</v>
       </c>
       <c r="H67">
-        <v>-149915295.021638</v>
-      </c>
-      <c r="I67">
-        <v>-321853774.78641135</v>
+        <v>-458852749.25256777</v>
+      </c>
+      <c r="J67">
+        <v>-160429456.52639863</v>
+      </c>
+      <c r="K67">
+        <v>-344426672.1584423</v>
       </c>
     </row>
     <row r="68">
@@ -6983,11 +8148,11 @@
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
-      <c r="C76">
+      <c r="D76">
         <v>0</v>
       </c>
-      <c r="F76">
-        <v>-14431385.829128567</v>
+      <c r="H76">
+        <v>-15443516.85500602</v>
       </c>
     </row>
     <row r="77">
@@ -6995,22 +8160,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>2066594.1052344</v>
+        <v>2384029.6349153505</v>
       </c>
       <c r="C77">
-        <v>2363340.1052344</v>
+        <v>2211532.646589267</v>
       </c>
       <c r="D77">
-        <v>-75299480.12035197</v>
-      </c>
-      <c r="F77">
-        <v>946326.6420157831</v>
+        <v>2529090.6349153505</v>
+      </c>
+      <c r="E77">
+        <v>-80580534.96599406</v>
       </c>
       <c r="H77">
-        <v>-249949429.30221963</v>
-      </c>
-      <c r="I77">
-        <v>-326426699.36305916</v>
+        <v>1012696.328637656</v>
+      </c>
+      <c r="J77">
+        <v>-267479386.25108847</v>
+      </c>
+      <c r="K77">
+        <v>-349320314.2945695</v>
       </c>
     </row>
     <row r="78">
@@ -7018,22 +8186,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-534683636.11797816</v>
+        <v>-579122931.5626874</v>
       </c>
       <c r="C78">
-        <v>-520553466.11797816</v>
+        <v>-572183146.113177</v>
       </c>
       <c r="D78">
-        <v>-436435494.5455228</v>
-      </c>
-      <c r="F78">
-        <v>-436399334.21864784</v>
+        <v>-557061970.5626874</v>
+      </c>
+      <c r="E78">
+        <v>-467044467.93545866</v>
       </c>
       <c r="H78">
-        <v>91817729.20504154</v>
-      </c>
-      <c r="I78">
-        <v>952847.4078616782</v>
+        <v>-467005771.5396871</v>
+      </c>
+      <c r="J78">
+        <v>98257275.17480296</v>
+      </c>
+      <c r="K78">
+        <v>1019674.4219712405</v>
       </c>
     </row>
     <row r="79">
@@ -7116,13 +8287,16 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B94">
-        <v>41132382.75522145</v>
+        <v>18684777.585636355</v>
       </c>
       <c r="C94">
-        <v>55256979.75522145</v>
-      </c>
-      <c r="F94">
-        <v>21103751.96308913</v>
+        <v>44017161.89201072</v>
+      </c>
+      <c r="D94">
+        <v>59132373.585636355</v>
+      </c>
+      <c r="H94">
+        <v>22583842.813487697</v>
       </c>
     </row>
     <row r="95">
@@ -7144,11 +8318,11 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="H98">
-        <v>8216405.07554006</v>
-      </c>
-      <c r="I98">
-        <v>3620077.16878612</v>
+      <c r="J98">
+        <v>8792654.549886853</v>
+      </c>
+      <c r="K98">
+        <v>3873967.7141558914</v>
       </c>
     </row>
     <row r="99">
@@ -7162,22 +8336,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>267825985.37593025</v>
+        <v>-366966653.31690705</v>
       </c>
       <c r="C101">
-        <v>-260319272.62406975</v>
+        <v>286609696.97125316</v>
       </c>
       <c r="D101">
-        <v>-262642754.67166927</v>
-      </c>
-      <c r="F101">
-        <v>-125779135.12063907</v>
+        <v>-278576508.31690705</v>
+      </c>
+      <c r="E101">
+        <v>-281062945.48858744</v>
       </c>
       <c r="H101">
-        <v>-153163269.57686755</v>
-      </c>
-      <c r="I101">
-        <v>-99516160.4789292</v>
+        <v>-134600530.8321082</v>
+      </c>
+      <c r="J101">
+        <v>-163905224.57682896</v>
+      </c>
+      <c r="K101">
+        <v>-106495628.34081826</v>
       </c>
     </row>
     <row r="102">
@@ -7225,14 +8402,17 @@
       <c r="C109">
         <v>0</v>
       </c>
-      <c r="F109">
-        <v>66905434.55457942</v>
+      <c r="D109">
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>234410896.22294948</v>
-      </c>
-      <c r="I109">
-        <v>796683105.6093335</v>
+        <v>71597781.28512155</v>
+      </c>
+      <c r="J109">
+        <v>250851073.46442467</v>
+      </c>
+      <c r="K109">
+        <v>852557690.2491581</v>
       </c>
     </row>
     <row r="110">
@@ -7240,22 +8420,25 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>520641.8955140631</v>
+        <v>358768.3563763029</v>
       </c>
       <c r="C110">
-        <v>-2751055.104485937</v>
+        <v>557156.6018673372</v>
       </c>
       <c r="D110">
-        <v>-19238368.563234475</v>
-      </c>
-      <c r="F110">
-        <v>-132951023.53498565</v>
+        <v>-2943997.643623697</v>
+      </c>
+      <c r="E110">
+        <v>-20587632.586847015</v>
       </c>
       <c r="H110">
-        <v>-332100390.03996176</v>
-      </c>
-      <c r="I110">
-        <v>-685521050.7412168</v>
+        <v>-142275412.57393134</v>
+      </c>
+      <c r="J110">
+        <v>-355391923.67680764</v>
+      </c>
+      <c r="K110">
+        <v>-733599394.1908697</v>
       </c>
     </row>
     <row r="111">
@@ -7273,13 +8456,16 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
-        <v>-39974890.871418126</v>
+        <v>-42946570.51125683</v>
       </c>
       <c r="C113">
-        <v>-38240497.871418126</v>
-      </c>
-      <c r="F113">
-        <v>-29579965.121464368</v>
+        <v>-42778490.45541392</v>
+      </c>
+      <c r="D113">
+        <v>-40922457.51125683</v>
+      </c>
+      <c r="H113">
+        <v>-31654526.830110393</v>
       </c>
     </row>
     <row r="114">
@@ -7301,17 +8487,20 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="C117">
-        <v>-218030094.27352747</v>
+      <c r="B117">
+        <v>-849624383.1102886</v>
       </c>
       <c r="D117">
-        <v>-48804174.22139108</v>
-      </c>
-      <c r="F117">
-        <v>-18940628.146249007</v>
-      </c>
-      <c r="I117">
-        <v>-150083629.04291373</v>
+        <v>-233321420.11028868</v>
+      </c>
+      <c r="E117">
+        <v>-52227006.89364192</v>
+      </c>
+      <c r="H117">
+        <v>-20269010.439079992</v>
+      </c>
+      <c r="K117">
+        <v>-160609596.48839697</v>
       </c>
     </row>
     <row r="118">
@@ -7319,13 +8508,16 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-1233182.0372438366</v>
+        <v>-1387418.8822580234</v>
       </c>
       <c r="C118">
-        <v>-1299353.0372438366</v>
-      </c>
-      <c r="F118">
-        <v>-8951937.711685406</v>
+        <v>-1319670.044371328</v>
+      </c>
+      <c r="D118">
+        <v>-1390481.8822580234</v>
+      </c>
+      <c r="H118">
+        <v>-9579773.04274774</v>
       </c>
     </row>
     <row r="119">
@@ -7353,22 +8545,25 @@
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
       <c r="B123">
-        <v>1340431.6626056172</v>
+        <v>571913.8305201957</v>
       </c>
       <c r="C123">
-        <v>1727.6626056171685</v>
+        <v>1434441.5165347715</v>
       </c>
       <c r="D123">
-        <v>-247879.767678882</v>
-      </c>
-      <c r="F123">
-        <v>-2261015.160834066</v>
+        <v>1848.8305201956819</v>
+      </c>
+      <c r="E123">
+        <v>-265264.5709490357</v>
       </c>
       <c r="H123">
-        <v>1942399.4595007156</v>
-      </c>
-      <c r="I123">
-        <v>318612.5685936767</v>
+        <v>-2419589.2313602953</v>
+      </c>
+      <c r="J123">
+        <v>2078627.7317460696</v>
+      </c>
+      <c r="K123">
+        <v>340958.14716294163</v>
       </c>
     </row>
     <row r="124">
@@ -7381,13 +8576,16 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>988519105.8315048</v>
+        <v>457880985.46994346</v>
       </c>
       <c r="C125">
-        <v>375509554.8315049</v>
-      </c>
-      <c r="F125">
-        <v>136831015.91763496</v>
+        <v>1057847919.330847</v>
+      </c>
+      <c r="D125">
+        <v>401845547.46994346</v>
+      </c>
+      <c r="H125">
+        <v>146427524.39938018</v>
       </c>
     </row>
     <row r="126">
@@ -7400,22 +8598,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>988519105.8315048</v>
+        <v>457880985.46994346</v>
       </c>
       <c r="C127">
-        <v>375509554.8315049</v>
+        <v>1057847919.330847</v>
       </c>
       <c r="D127">
-        <v>27721111.562416106</v>
-      </c>
-      <c r="F127">
-        <v>136831015.91763496</v>
+        <v>401845547.46994346</v>
+      </c>
+      <c r="E127">
+        <v>29665304.408227205</v>
       </c>
       <c r="H127">
-        <v>20880123.841548815</v>
-      </c>
-      <c r="I127">
-        <v>121699370.94631772</v>
+        <v>146427524.39938018</v>
+      </c>
+      <c r="J127">
+        <v>22344530.753984</v>
+      </c>
+      <c r="K127">
+        <v>130234636.4172136</v>
       </c>
     </row>
     <row r="128">
@@ -7423,13 +8624,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>520596454.64008915</v>
+        <v>557107973.5677843</v>
       </c>
       <c r="C128">
-        <v>189907621.64008912</v>
-      </c>
-      <c r="F128">
-        <v>76631353.00893886</v>
+        <v>557107974.0424399</v>
+      </c>
+      <c r="D128">
+        <v>203226605.56778425</v>
+      </c>
+      <c r="H128">
+        <v>82005817.44732732</v>
       </c>
     </row>
     <row r="129">
@@ -7437,18 +8641,21 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>1434149162.3058848</v>
+        <v>912048016.8250648</v>
       </c>
       <c r="C129">
-        <v>520596456.30588496</v>
-      </c>
-      <c r="F129">
-        <v>189907621.64008912</v>
+        <v>1534731800.736639</v>
+      </c>
+      <c r="D129">
+        <v>557107975.8250648</v>
+      </c>
+      <c r="H129">
+        <v>203226605.56778425</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>